--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB720F09-F99B-4759-8E4C-E1B968D88BDA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756D7CBE-3287-47D9-9854-D33DC6BC1740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$142</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1101,7 +1093,8 @@
     <col min="25" max="34" width="6.5703125" customWidth="1"/>
     <col min="35" max="35" width="29.42578125" customWidth="1"/>
     <col min="36" max="37" width="7" customWidth="1"/>
-    <col min="38" max="46" width="3" customWidth="1"/>
+    <col min="38" max="38" width="7.5703125" customWidth="1"/>
+    <col min="39" max="46" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -1654,7 +1647,10 @@
         <f>ROUND(G6*V6,0)</f>
         <v>1090</v>
       </c>
-      <c r="AL6" s="1"/>
+      <c r="AL6" s="1">
+        <f>(SUM(Y6:AH6)+R6)/11*7</f>
+        <v>3953.4514727272722</v>
+      </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
@@ -1774,7 +1770,10 @@
         <f t="shared" ref="AK7:AK70" si="12">ROUND(G7*V7,0)</f>
         <v>608</v>
       </c>
-      <c r="AL7" s="1"/>
+      <c r="AL7" s="1">
+        <f t="shared" ref="AL7:AL70" si="13">(SUM(Y7:AH7)+R7)/11*7</f>
+        <v>1628.8961818181815</v>
+      </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
@@ -1894,7 +1893,10 @@
         <f t="shared" si="12"/>
         <v>452</v>
       </c>
-      <c r="AL8" s="1"/>
+      <c r="AL8" s="1">
+        <f t="shared" si="13"/>
+        <v>1520.5870909090911</v>
+      </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
@@ -1941,7 +1943,7 @@
       </c>
       <c r="S9" s="12"/>
       <c r="T9" s="5">
-        <f t="shared" ref="T9:T69" si="13">S9</f>
+        <f t="shared" ref="T9:T69" si="14">S9</f>
         <v>0</v>
       </c>
       <c r="U9" s="5">
@@ -1998,7 +2000,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL9" s="1"/>
+      <c r="AL9" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
@@ -2056,11 +2061,11 @@
         <v>136.80000000000001</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" ref="S10:S12" si="14">12*R10-Q10-P10-O10-F10</f>
+        <f t="shared" ref="S10:S12" si="15">12*R10-Q10-P10-O10-F10</f>
         <v>770.97000000000025</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" ref="T10:T11" si="15">S10+$T$1*R10</f>
+        <f t="shared" ref="T10:T11" si="16">S10+$T$1*R10</f>
         <v>736.08600000000024</v>
       </c>
       <c r="U10" s="5">
@@ -2068,7 +2073,7 @@
         <v>271.46851680000009</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" ref="V10:V11" si="16">T10*$V$1</f>
+        <f t="shared" ref="V10:V11" si="17">T10*$V$1</f>
         <v>464.61748320000015</v>
       </c>
       <c r="W10" s="1">
@@ -2118,7 +2123,10 @@
         <f t="shared" si="12"/>
         <v>209</v>
       </c>
-      <c r="AL10" s="1"/>
+      <c r="AL10" s="1">
+        <f t="shared" si="13"/>
+        <v>814.29090909090905</v>
+      </c>
       <c r="AM10" s="1"/>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
@@ -2176,11 +2184,11 @@
         <v>246.4</v>
       </c>
       <c r="S11" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1295.9700000000012</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1233.1380000000011</v>
       </c>
       <c r="U11" s="5">
@@ -2188,7 +2196,7 @@
         <v>454.78129440000043</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>778.35670560000062</v>
       </c>
       <c r="W11" s="1">
@@ -2238,7 +2246,10 @@
         <f t="shared" si="12"/>
         <v>350</v>
       </c>
-      <c r="AL11" s="1"/>
+      <c r="AL11" s="1">
+        <f t="shared" si="13"/>
+        <v>1518.3636363636363</v>
+      </c>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
@@ -2294,11 +2305,11 @@
         <v>20.2</v>
       </c>
       <c r="S12" s="5">
+        <f t="shared" si="15"/>
+        <v>122.19999999999999</v>
+      </c>
+      <c r="T12" s="5">
         <f t="shared" si="14"/>
-        <v>122.19999999999999</v>
-      </c>
-      <c r="T12" s="5">
-        <f t="shared" si="13"/>
         <v>122.19999999999999</v>
       </c>
       <c r="U12" s="5">
@@ -2353,7 +2364,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="1"/>
+      <c r="AL12" s="1">
+        <f t="shared" si="13"/>
+        <v>106.27272727272725</v>
+      </c>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
@@ -2404,7 +2418,7 @@
       </c>
       <c r="S13" s="12"/>
       <c r="T13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U13" s="5">
@@ -2459,7 +2473,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="1"/>
+      <c r="AL13" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
@@ -2517,11 +2534,11 @@
         <v>17.600000000000001</v>
       </c>
       <c r="S14" s="5">
-        <f t="shared" ref="S14:S15" si="17">12*R14-Q14-P14-O14-F14</f>
+        <f t="shared" ref="S14:S15" si="18">12*R14-Q14-P14-O14-F14</f>
         <v>67.400000000000006</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>67.400000000000006</v>
       </c>
       <c r="U14" s="5">
@@ -2576,7 +2593,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="1"/>
+      <c r="AL14" s="1">
+        <f t="shared" si="13"/>
+        <v>103.85454545454544</v>
+      </c>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
@@ -2634,11 +2654,11 @@
         <v>56</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>159.10000000000002</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>159.10000000000002</v>
       </c>
       <c r="U15" s="5">
@@ -2693,7 +2713,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="1"/>
+      <c r="AL15" s="1">
+        <f t="shared" si="13"/>
+        <v>334.21818181818185</v>
+      </c>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
@@ -2746,7 +2769,7 @@
       </c>
       <c r="S16" s="12"/>
       <c r="T16" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U16" s="5">
@@ -2801,7 +2824,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="1"/>
+      <c r="AL16" s="1">
+        <f t="shared" si="13"/>
+        <v>0.50909090909090915</v>
+      </c>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
@@ -2852,7 +2878,7 @@
       </c>
       <c r="S17" s="12"/>
       <c r="T17" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U17" s="5">
@@ -2907,7 +2933,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="1"/>
+      <c r="AL17" s="1">
+        <f t="shared" si="13"/>
+        <v>0.76363636363636378</v>
+      </c>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
@@ -2965,11 +2994,11 @@
         <v>227.60939999999999</v>
       </c>
       <c r="S18" s="5">
-        <f t="shared" ref="S18:S20" si="18">12*R18-Q18-P18-O18-F18</f>
+        <f t="shared" ref="S18:S20" si="19">12*R18-Q18-P18-O18-F18</f>
         <v>1023.6185521999998</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:T19" si="19">S18+$T$1*R18</f>
+        <f t="shared" ref="T18:T19" si="20">S18+$T$1*R18</f>
         <v>965.57815519999986</v>
       </c>
       <c r="U18" s="5">
@@ -2977,7 +3006,7 @@
         <v>356.10522363775999</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" ref="V18:V19" si="20">T18*$V$1</f>
+        <f t="shared" ref="V18:V19" si="21">T18*$V$1</f>
         <v>609.47293156223986</v>
       </c>
       <c r="W18" s="1">
@@ -3027,7 +3056,10 @@
         <f t="shared" si="12"/>
         <v>609</v>
       </c>
-      <c r="AL18" s="1"/>
+      <c r="AL18" s="1">
+        <f t="shared" si="13"/>
+        <v>1603.7039454545452</v>
+      </c>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
@@ -3085,11 +3117,11 @@
         <v>779.79539999999997</v>
       </c>
       <c r="S19" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3395.7145479999999</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3196.8667209999999</v>
       </c>
       <c r="U19" s="5">
@@ -3097,7 +3129,7 @@
         <v>1179.0044467048001</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2017.8622742951998</v>
       </c>
       <c r="W19" s="1">
@@ -3147,7 +3179,10 @@
         <f t="shared" si="12"/>
         <v>2018</v>
       </c>
-      <c r="AL19" s="1"/>
+      <c r="AL19" s="1">
+        <f t="shared" si="13"/>
+        <v>4989.3374363636358</v>
+      </c>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
@@ -3205,11 +3240,11 @@
         <v>20.923999999999999</v>
       </c>
       <c r="S20" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>89.22799999999998</v>
       </c>
       <c r="T20" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>89.22799999999998</v>
       </c>
       <c r="U20" s="5">
@@ -3264,7 +3299,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="1"/>
+      <c r="AL20" s="1">
+        <f t="shared" si="13"/>
+        <v>137.84527272727274</v>
+      </c>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
@@ -3319,7 +3357,7 @@
       </c>
       <c r="S21" s="12"/>
       <c r="T21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U21" s="5">
@@ -3376,7 +3414,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="1"/>
+      <c r="AL21" s="1">
+        <f t="shared" si="13"/>
+        <v>518.14789090909085</v>
+      </c>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
@@ -3434,11 +3475,11 @@
         <v>14.416599999999999</v>
       </c>
       <c r="S22" s="5">
-        <f t="shared" ref="S22:S26" si="21">12*R22-Q22-P22-O22-F22</f>
+        <f t="shared" ref="S22:S26" si="22">12*R22-Q22-P22-O22-F22</f>
         <v>22.206800000000015</v>
       </c>
       <c r="T22" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.206800000000015</v>
       </c>
       <c r="U22" s="5">
@@ -3493,7 +3534,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="1"/>
+      <c r="AL22" s="1">
+        <f t="shared" si="13"/>
+        <v>108.11194545454543</v>
+      </c>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
@@ -3552,7 +3596,7 @@
       </c>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U23" s="5">
@@ -3607,7 +3651,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="1"/>
+      <c r="AL23" s="1">
+        <f t="shared" si="13"/>
+        <v>10.785727272727271</v>
+      </c>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
@@ -3665,7 +3712,7 @@
         <v>282.6728</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1281.7909242000017</v>
       </c>
       <c r="T24" s="5">
@@ -3727,7 +3774,10 @@
         <f t="shared" si="12"/>
         <v>764</v>
       </c>
-      <c r="AL24" s="1"/>
+      <c r="AL24" s="1">
+        <f t="shared" si="13"/>
+        <v>2008.0753636363638</v>
+      </c>
       <c r="AM24" s="1"/>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
@@ -3785,11 +3835,11 @@
         <v>41.240400000000001</v>
       </c>
       <c r="S25" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>131.13319999999999</v>
       </c>
       <c r="T25" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>131.13319999999999</v>
       </c>
       <c r="U25" s="5">
@@ -3844,7 +3894,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="1"/>
+      <c r="AL25" s="1">
+        <f t="shared" si="13"/>
+        <v>271.57047272727272</v>
+      </c>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
@@ -3902,11 +3955,11 @@
         <v>90.167400000000001</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>331.63761999999974</v>
       </c>
       <c r="T26" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>331.63761999999974</v>
       </c>
       <c r="U26" s="5">
@@ -3964,7 +4017,10 @@
         <f t="shared" si="12"/>
         <v>209</v>
       </c>
-      <c r="AL26" s="1"/>
+      <c r="AL26" s="1">
+        <f t="shared" si="13"/>
+        <v>666.84061818181817</v>
+      </c>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
@@ -4011,7 +4067,7 @@
       </c>
       <c r="S27" s="12"/>
       <c r="T27" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U27" s="5">
@@ -4068,7 +4124,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="1"/>
+      <c r="AL27" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM27" s="1"/>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
@@ -4126,7 +4185,7 @@
         <v>138.39000000000001</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" ref="S28:S29" si="22">12*R28-Q28-P28-O28-F28</f>
+        <f t="shared" ref="S28:S29" si="23">12*R28-Q28-P28-O28-F28</f>
         <v>530.51236600000038</v>
       </c>
       <c r="T28" s="5">
@@ -4188,7 +4247,10 @@
         <f t="shared" si="12"/>
         <v>313</v>
       </c>
-      <c r="AL28" s="1"/>
+      <c r="AL28" s="1">
+        <f t="shared" si="13"/>
+        <v>917.06821818181834</v>
+      </c>
       <c r="AM28" s="1"/>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
@@ -4246,11 +4308,11 @@
         <v>28.8462</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>119.8202000000001</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>119.8202000000001</v>
       </c>
       <c r="U29" s="5">
@@ -4305,7 +4367,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="1"/>
+      <c r="AL29" s="1">
+        <f t="shared" si="13"/>
+        <v>112.12994545454544</v>
+      </c>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
@@ -4356,7 +4421,7 @@
       </c>
       <c r="S30" s="12"/>
       <c r="T30" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U30" s="5">
@@ -4411,7 +4476,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="1"/>
+      <c r="AL30" s="1">
+        <f t="shared" si="13"/>
+        <v>0.44749090909090916</v>
+      </c>
       <c r="AM30" s="1"/>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
@@ -4469,11 +4537,11 @@
         <v>56.640599999999992</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" ref="S31:S33" si="23">12*R31-Q31-P31-O31-F31</f>
+        <f t="shared" ref="S31:S33" si="24">12*R31-Q31-P31-O31-F31</f>
         <v>199.09309999999959</v>
       </c>
       <c r="T31" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>199.09309999999959</v>
       </c>
       <c r="U31" s="5">
@@ -4528,7 +4596,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="1"/>
+      <c r="AL31" s="1">
+        <f t="shared" si="13"/>
+        <v>334.69125454545457</v>
+      </c>
       <c r="AM31" s="1"/>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
@@ -4586,11 +4657,11 @@
         <v>44.1312</v>
       </c>
       <c r="S32" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>164.97571200000007</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>164.97571200000007</v>
       </c>
       <c r="U32" s="5">
@@ -4645,7 +4716,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="1"/>
+      <c r="AL32" s="1">
+        <f t="shared" si="13"/>
+        <v>274.72009090909086</v>
+      </c>
       <c r="AM32" s="1"/>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
@@ -4703,7 +4777,7 @@
         <v>450.7</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3339.9273359999997</v>
       </c>
       <c r="T33" s="5">
@@ -4765,7 +4839,10 @@
         <f t="shared" si="12"/>
         <v>2036</v>
       </c>
-      <c r="AL33" s="1"/>
+      <c r="AL33" s="1">
+        <f t="shared" si="13"/>
+        <v>2974.8495636363632</v>
+      </c>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
@@ -4824,7 +4901,7 @@
       </c>
       <c r="S34" s="12"/>
       <c r="T34" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U34" s="5">
@@ -4879,7 +4956,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="1"/>
+      <c r="AL34" s="1">
+        <f t="shared" si="13"/>
+        <v>30.380509090909086</v>
+      </c>
       <c r="AM34" s="1"/>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
@@ -4938,7 +5018,7 @@
       </c>
       <c r="S35" s="12"/>
       <c r="T35" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U35" s="5">
@@ -4993,7 +5073,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="1"/>
+      <c r="AL35" s="1">
+        <f t="shared" si="13"/>
+        <v>70.229345454545452</v>
+      </c>
       <c r="AM35" s="1"/>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
@@ -5115,7 +5198,10 @@
         <f t="shared" si="12"/>
         <v>2340</v>
       </c>
-      <c r="AL36" s="1"/>
+      <c r="AL36" s="1">
+        <f t="shared" si="13"/>
+        <v>3597.5668909090914</v>
+      </c>
       <c r="AM36" s="1"/>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
@@ -5162,7 +5248,7 @@
       </c>
       <c r="S37" s="12"/>
       <c r="T37" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U37" s="5">
@@ -5219,7 +5305,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL37" s="1"/>
+      <c r="AL37" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
@@ -5262,7 +5351,7 @@
         <v>259.2</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="24">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="25">E38-K38</f>
         <v>-26.278999999999996</v>
       </c>
       <c r="M38" s="1"/>
@@ -5273,7 +5362,7 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1">
-        <f t="shared" ref="R38:R69" si="25">E38/5</f>
+        <f t="shared" ref="R38:R69" si="26">E38/5</f>
         <v>46.584199999999996</v>
       </c>
       <c r="S38" s="5">
@@ -5281,7 +5370,7 @@
         <v>9.3594639999999742</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.3594639999999742</v>
       </c>
       <c r="U38" s="5">
@@ -5294,7 +5383,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="X38" s="1">
-        <f t="shared" ref="X38:X69" si="26">(F38+O38+P38+Q38)/R38</f>
+        <f t="shared" ref="X38:X69" si="27">(F38+O38+P38+Q38)/R38</f>
         <v>11.799085011656311</v>
       </c>
       <c r="Y38" s="1">
@@ -5336,7 +5425,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL38" s="1"/>
+      <c r="AL38" s="1">
+        <f t="shared" si="13"/>
+        <v>341.42296363636365</v>
+      </c>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
@@ -5367,7 +5459,7 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M39" s="10"/>
@@ -5378,12 +5470,12 @@
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S39" s="12"/>
       <c r="T39" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U39" s="5">
@@ -5396,7 +5488,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X39" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y39" s="10">
@@ -5440,7 +5532,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL39" s="1"/>
+      <c r="AL39" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
@@ -5471,7 +5566,7 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M40" s="10"/>
@@ -5482,12 +5577,12 @@
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S40" s="12"/>
       <c r="T40" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U40" s="5">
@@ -5500,7 +5595,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X40" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y40" s="10">
@@ -5544,7 +5639,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="1"/>
+      <c r="AL40" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
@@ -5587,7 +5685,7 @@
         <v>4451</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-54</v>
       </c>
       <c r="M41" s="1"/>
@@ -5600,7 +5698,7 @@
       </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>879.4</v>
       </c>
       <c r="S41" s="5">
@@ -5608,7 +5706,7 @@
         <v>5753.1833020000031</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" ref="T41:T43" si="27">S41+$T$1*R41</f>
+        <f t="shared" ref="T41:T43" si="28">S41+$T$1*R41</f>
         <v>5528.9363020000028</v>
       </c>
       <c r="U41" s="5">
@@ -5616,7 +5714,7 @@
         <v>2039.0717081776011</v>
       </c>
       <c r="V41" s="5">
-        <f t="shared" ref="V41:V43" si="28">T41*$V$1</f>
+        <f t="shared" ref="V41:V43" si="29">T41*$V$1</f>
         <v>3489.8645938224017</v>
       </c>
       <c r="W41" s="1">
@@ -5624,7 +5722,7 @@
         <v>8.7449999999999974</v>
       </c>
       <c r="X41" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2.4578311325903974</v>
       </c>
       <c r="Y41" s="1">
@@ -5666,7 +5764,10 @@
         <f t="shared" si="12"/>
         <v>1396</v>
       </c>
-      <c r="AL41" s="1"/>
+      <c r="AL41" s="1">
+        <f t="shared" si="13"/>
+        <v>6099.4927636363636</v>
+      </c>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
@@ -5709,7 +5810,7 @@
         <v>513</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4</v>
       </c>
       <c r="M42" s="1"/>
@@ -5720,15 +5821,15 @@
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>101.8</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" ref="S42:S61" si="29">12*R42-Q42-P42-O42-F42</f>
+        <f t="shared" ref="S42:S61" si="30">12*R42-Q42-P42-O42-F42</f>
         <v>564.92999999999984</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>538.97099999999989</v>
       </c>
       <c r="U42" s="5">
@@ -5736,7 +5837,7 @@
         <v>198.77250479999998</v>
       </c>
       <c r="V42" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>340.19849519999991</v>
       </c>
       <c r="W42" s="1">
@@ -5744,7 +5845,7 @@
         <v>11.745000000000001</v>
       </c>
       <c r="X42" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.4505893909626728</v>
       </c>
       <c r="Y42" s="1">
@@ -5786,7 +5887,10 @@
         <f t="shared" si="12"/>
         <v>153</v>
       </c>
-      <c r="AL42" s="1"/>
+      <c r="AL42" s="1">
+        <f t="shared" si="13"/>
+        <v>667.16363636363644</v>
+      </c>
       <c r="AM42" s="1"/>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
@@ -5829,7 +5933,7 @@
         <v>1121</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-27</v>
       </c>
       <c r="M43" s="1"/>
@@ -5840,15 +5944,15 @@
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>218.8</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1669.3888000000015</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1613.5948000000014</v>
       </c>
       <c r="U43" s="5">
@@ -5856,7 +5960,7 @@
         <v>595.09376224000061</v>
       </c>
       <c r="V43" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1018.5010377600008</v>
       </c>
       <c r="W43" s="1">
@@ -5864,7 +5968,7 @@
         <v>11.744999999999999</v>
       </c>
       <c r="X43" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.3702522851919499</v>
       </c>
       <c r="Y43" s="1">
@@ -5906,7 +6010,10 @@
         <f t="shared" si="12"/>
         <v>407</v>
       </c>
-      <c r="AL43" s="1"/>
+      <c r="AL43" s="1">
+        <f t="shared" si="13"/>
+        <v>1560.1090909090908</v>
+      </c>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
@@ -5947,7 +6054,7 @@
         <v>20</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M44" s="1"/>
@@ -5958,7 +6065,7 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
       <c r="S44" s="5">
@@ -5966,7 +6073,7 @@
         <v>28</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="U44" s="5">
@@ -5979,7 +6086,7 @@
         <v>9</v>
       </c>
       <c r="X44" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2</v>
       </c>
       <c r="Y44" s="1">
@@ -6021,7 +6128,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL44" s="1"/>
+      <c r="AL44" s="1">
+        <f t="shared" si="13"/>
+        <v>13.236363636363636</v>
+      </c>
       <c r="AM44" s="1"/>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
@@ -6064,7 +6174,7 @@
         <v>261.61</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>14.036999999999978</v>
       </c>
       <c r="M45" s="1"/>
@@ -6075,15 +6185,15 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>55.129399999999997</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>289.80657800000006</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>289.80657800000006</v>
       </c>
       <c r="U45" s="5">
@@ -6096,7 +6206,7 @@
         <v>12</v>
       </c>
       <c r="X45" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.7431574078440883</v>
       </c>
       <c r="Y45" s="1">
@@ -6138,7 +6248,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL45" s="1"/>
+      <c r="AL45" s="1">
+        <f t="shared" si="13"/>
+        <v>390.7804727272727</v>
+      </c>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
@@ -6179,7 +6292,7 @@
         <v>301</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M46" s="1"/>
@@ -6190,12 +6303,12 @@
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>60.2</v>
       </c>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U46" s="5">
@@ -6208,7 +6321,7 @@
         <v>18.637873754152825</v>
       </c>
       <c r="X46" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.637873754152825</v>
       </c>
       <c r="Y46" s="1">
@@ -6252,7 +6365,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL46" s="1"/>
+      <c r="AL46" s="1">
+        <f t="shared" si="13"/>
+        <v>374.69090909090914</v>
+      </c>
       <c r="AM46" s="1"/>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
@@ -6295,7 +6411,7 @@
         <v>255</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-17</v>
       </c>
       <c r="M47" s="1"/>
@@ -6306,15 +6422,15 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>47.6</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>287.34400000000016</v>
       </c>
       <c r="T47" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>287.34400000000016</v>
       </c>
       <c r="U47" s="5">
@@ -6327,7 +6443,7 @@
         <v>12</v>
       </c>
       <c r="X47" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.9633613445378124</v>
       </c>
       <c r="Y47" s="1">
@@ -6369,7 +6485,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL47" s="1"/>
+      <c r="AL47" s="1">
+        <f t="shared" si="13"/>
+        <v>352.16363636363644</v>
+      </c>
       <c r="AM47" s="1"/>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
@@ -6412,7 +6531,7 @@
         <v>40.15</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2.3699999999999974</v>
       </c>
       <c r="M48" s="1"/>
@@ -6423,15 +6542,15 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.556</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>14.721999999999994</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.721999999999994</v>
       </c>
       <c r="U48" s="5">
@@ -6444,7 +6563,7 @@
         <v>12</v>
       </c>
       <c r="X48" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.051614610905242</v>
       </c>
       <c r="Y48" s="1">
@@ -6486,7 +6605,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL48" s="1"/>
+      <c r="AL48" s="1">
+        <f t="shared" si="13"/>
+        <v>61.542854545454546</v>
+      </c>
       <c r="AM48" s="1"/>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
@@ -6529,7 +6651,7 @@
         <v>225</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-74</v>
       </c>
       <c r="M49" s="1"/>
@@ -6542,7 +6664,7 @@
       </c>
       <c r="Q49" s="1"/>
       <c r="R49" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>30.2</v>
       </c>
       <c r="S49" s="5">
@@ -6550,7 +6672,7 @@
         <v>232.49199999999993</v>
       </c>
       <c r="T49" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>232.49199999999993</v>
       </c>
       <c r="U49" s="5">
@@ -6563,7 +6685,7 @@
         <v>6.9999999999999991</v>
       </c>
       <c r="X49" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-0.69841059602648858</v>
       </c>
       <c r="Y49" s="1">
@@ -6605,7 +6727,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL49" s="1"/>
+      <c r="AL49" s="1">
+        <f t="shared" si="13"/>
+        <v>294.76363636363635</v>
+      </c>
       <c r="AM49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
@@ -6648,7 +6773,7 @@
         <v>297</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-84</v>
       </c>
       <c r="M50" s="1"/>
@@ -6661,7 +6786,7 @@
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42.6</v>
       </c>
       <c r="S50" s="5">
@@ -6669,7 +6794,7 @@
         <v>279.99600000000004</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>279.99600000000004</v>
       </c>
       <c r="U50" s="5">
@@ -6682,7 +6807,7 @@
         <v>7.0000000000000009</v>
       </c>
       <c r="X50" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.42732394366197202</v>
       </c>
       <c r="Y50" s="1">
@@ -6724,7 +6849,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL50" s="1"/>
+      <c r="AL50" s="1">
+        <f t="shared" si="13"/>
+        <v>288.78181818181821</v>
+      </c>
       <c r="AM50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
@@ -6767,7 +6895,7 @@
         <v>131.44999999999999</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-8.8999999999999915</v>
       </c>
       <c r="M51" s="1"/>
@@ -6778,15 +6906,15 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>24.509999999999998</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>70.743599999999958</v>
       </c>
       <c r="T51" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>70.743599999999958</v>
       </c>
       <c r="U51" s="5">
@@ -6799,7 +6927,7 @@
         <v>12.000000000000002</v>
       </c>
       <c r="X51" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.1136842105263192</v>
       </c>
       <c r="Y51" s="1">
@@ -6841,7 +6969,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL51" s="1"/>
+      <c r="AL51" s="1">
+        <f t="shared" si="13"/>
+        <v>174.75207272727275</v>
+      </c>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
@@ -6884,7 +7015,7 @@
         <v>1396</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-35</v>
       </c>
       <c r="M52" s="1"/>
@@ -6895,15 +7026,15 @@
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>272.2</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>797.21659999999929</v>
       </c>
       <c r="T52" s="5">
-        <f t="shared" ref="T52:T53" si="30">S52+$T$1*R52</f>
+        <f t="shared" ref="T52:T53" si="31">S52+$T$1*R52</f>
         <v>727.80559999999923</v>
       </c>
       <c r="U52" s="5">
@@ -6911,7 +7042,7 @@
         <v>268.41470527999974</v>
       </c>
       <c r="V52" s="5">
-        <f t="shared" ref="V52:V53" si="31">T52*$V$1</f>
+        <f t="shared" ref="V52:V53" si="32">T52*$V$1</f>
         <v>459.39089471999949</v>
       </c>
       <c r="W52" s="1">
@@ -6919,7 +7050,7 @@
         <v>11.744999999999999</v>
       </c>
       <c r="X52" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.0712101396032345</v>
       </c>
       <c r="Y52" s="1">
@@ -6961,7 +7092,10 @@
         <f t="shared" si="12"/>
         <v>161</v>
       </c>
-      <c r="AL52" s="1"/>
+      <c r="AL52" s="1">
+        <f t="shared" si="13"/>
+        <v>2203.9818181818177</v>
+      </c>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
@@ -7004,7 +7138,7 @@
         <v>740</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-23</v>
       </c>
       <c r="M53" s="1"/>
@@ -7017,7 +7151,7 @@
       </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>143.4</v>
       </c>
       <c r="S53" s="5">
@@ -7025,7 +7159,7 @@
         <v>1052.5479999999995</v>
       </c>
       <c r="T53" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1015.9809999999995</v>
       </c>
       <c r="U53" s="5">
@@ -7033,7 +7167,7 @@
         <v>374.69379279999987</v>
       </c>
       <c r="V53" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>641.28720719999967</v>
       </c>
       <c r="W53" s="1">
@@ -7041,7 +7175,7 @@
         <v>8.745000000000001</v>
       </c>
       <c r="X53" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.6600557880055828</v>
       </c>
       <c r="Y53" s="1">
@@ -7083,7 +7217,10 @@
         <f t="shared" si="12"/>
         <v>257</v>
       </c>
-      <c r="AL53" s="1"/>
+      <c r="AL53" s="1">
+        <f t="shared" si="13"/>
+        <v>857.69090909090926</v>
+      </c>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
@@ -7126,7 +7263,7 @@
         <v>488.45</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.5799999999999841</v>
       </c>
       <c r="M54" s="1"/>
@@ -7137,15 +7274,15 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>98.405999999999992</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>243.17205800000022</v>
       </c>
       <c r="T54" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>243.17205800000022</v>
       </c>
       <c r="U54" s="5">
@@ -7158,7 +7295,7 @@
         <v>12</v>
       </c>
       <c r="X54" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.5288899254110504</v>
       </c>
       <c r="Y54" s="1">
@@ -7200,7 +7337,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL54" s="1"/>
+      <c r="AL54" s="1">
+        <f t="shared" si="13"/>
+        <v>697.95180000000005</v>
+      </c>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
@@ -7243,7 +7383,7 @@
         <v>603.85</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.8089999999999691</v>
       </c>
       <c r="M55" s="1"/>
@@ -7254,15 +7394,15 @@
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>121.9318</v>
       </c>
       <c r="S55" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>96.968599999999924</v>
       </c>
       <c r="T55" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96.968599999999924</v>
       </c>
       <c r="U55" s="5">
@@ -7275,7 +7415,7 @@
         <v>12</v>
       </c>
       <c r="X55" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.204730841339176</v>
       </c>
       <c r="Y55" s="1">
@@ -7317,7 +7457,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL55" s="1"/>
+      <c r="AL55" s="1">
+        <f t="shared" si="13"/>
+        <v>825.48161818181825</v>
+      </c>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
@@ -7360,7 +7503,7 @@
         <v>52.6</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.7269999999999968</v>
       </c>
       <c r="M56" s="1"/>
@@ -7371,15 +7514,15 @@
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11.0654</v>
       </c>
       <c r="S56" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>81.430800000000019</v>
       </c>
       <c r="T56" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>81.430800000000019</v>
       </c>
       <c r="U56" s="5">
@@ -7392,7 +7535,7 @@
         <v>12.000000000000002</v>
       </c>
       <c r="X56" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.6409528801489328</v>
       </c>
       <c r="Y56" s="1">
@@ -7434,7 +7577,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL56" s="1"/>
+      <c r="AL56" s="1">
+        <f t="shared" si="13"/>
+        <v>51.887563636363623</v>
+      </c>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
@@ -7477,7 +7623,7 @@
         <v>238</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-7</v>
       </c>
       <c r="M57" s="1"/>
@@ -7488,12 +7634,12 @@
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>46.2</v>
       </c>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U57" s="5">
@@ -7506,7 +7652,7 @@
         <v>12.597402597402597</v>
       </c>
       <c r="X57" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.597402597402597</v>
       </c>
       <c r="Y57" s="1">
@@ -7548,7 +7694,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL57" s="1"/>
+      <c r="AL57" s="1">
+        <f t="shared" si="13"/>
+        <v>418.6</v>
+      </c>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
@@ -7591,7 +7740,7 @@
         <v>523</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-6</v>
       </c>
       <c r="M58" s="1"/>
@@ -7602,11 +7751,11 @@
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>103.4</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>568.80000000000018</v>
       </c>
       <c r="T58" s="5">
@@ -7626,7 +7775,7 @@
         <v>11.745000000000001</v>
       </c>
       <c r="X58" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.4990328820116048</v>
       </c>
       <c r="Y58" s="1">
@@ -7668,7 +7817,10 @@
         <f t="shared" si="12"/>
         <v>154</v>
       </c>
-      <c r="AL58" s="1"/>
+      <c r="AL58" s="1">
+        <f t="shared" si="13"/>
+        <v>706.36363636363637</v>
+      </c>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
@@ -7711,7 +7863,7 @@
         <v>139</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M59" s="1"/>
@@ -7724,15 +7876,15 @@
       </c>
       <c r="Q59" s="1"/>
       <c r="R59" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>27.4</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>64.199999999999932</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>64.199999999999932</v>
       </c>
       <c r="U59" s="5">
@@ -7745,7 +7897,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="X59" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.6569343065693438</v>
       </c>
       <c r="Y59" s="1">
@@ -7787,7 +7939,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL59" s="1"/>
+      <c r="AL59" s="1">
+        <f t="shared" si="13"/>
+        <v>185.69090909090906</v>
+      </c>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
@@ -7830,7 +7985,7 @@
         <v>91</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5</v>
       </c>
       <c r="M60" s="1"/>
@@ -7843,7 +7998,7 @@
       </c>
       <c r="Q60" s="1"/>
       <c r="R60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.2</v>
       </c>
       <c r="S60" s="5">
@@ -7851,7 +8006,7 @@
         <v>128.39999999999998</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>128.39999999999998</v>
       </c>
       <c r="U60" s="5">
@@ -7864,7 +8019,7 @@
         <v>7.9999999999999982</v>
       </c>
       <c r="X60" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.53488372093023273</v>
       </c>
       <c r="Y60" s="1">
@@ -7906,7 +8061,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL60" s="1"/>
+      <c r="AL60" s="1">
+        <f t="shared" si="13"/>
+        <v>80.181818181818187</v>
+      </c>
       <c r="AM60" s="1"/>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
@@ -7949,7 +8107,7 @@
         <v>770.44</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-7.5520000000000209</v>
       </c>
       <c r="M61" s="1"/>
@@ -7960,15 +8118,15 @@
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>152.57760000000002</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>295.69120000000021</v>
       </c>
       <c r="T61" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>295.69120000000021</v>
       </c>
       <c r="U61" s="5">
@@ -7981,7 +8139,7 @@
         <v>12</v>
       </c>
       <c r="X61" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.062027453571165</v>
       </c>
       <c r="Y61" s="1">
@@ -8023,7 +8181,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL61" s="1"/>
+      <c r="AL61" s="1">
+        <f t="shared" si="13"/>
+        <v>1043.6063272727272</v>
+      </c>
       <c r="AM61" s="1"/>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
@@ -8060,7 +8221,7 @@
       </c>
       <c r="K62" s="10"/>
       <c r="L62" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M62" s="10"/>
@@ -8069,12 +8230,12 @@
       <c r="P62" s="10"/>
       <c r="Q62" s="10"/>
       <c r="R62" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S62" s="12"/>
       <c r="T62" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U62" s="5">
@@ -8087,7 +8248,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X62" s="10" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y62" s="10">
@@ -8129,7 +8290,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL62" s="1"/>
+      <c r="AL62" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM62" s="1"/>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
@@ -8170,7 +8334,7 @@
         <v>215</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M63" s="1"/>
@@ -8181,12 +8345,12 @@
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>43</v>
       </c>
       <c r="S63" s="5"/>
       <c r="T63" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U63" s="5">
@@ -8199,7 +8363,7 @@
         <v>12.767441860465116</v>
       </c>
       <c r="X63" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.767441860465116</v>
       </c>
       <c r="Y63" s="1">
@@ -8243,7 +8407,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL63" s="1"/>
+      <c r="AL63" s="1">
+        <f t="shared" si="13"/>
+        <v>230.4909090909091</v>
+      </c>
       <c r="AM63" s="1"/>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
@@ -8286,7 +8453,7 @@
         <v>966.25</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>24.971000000000004</v>
       </c>
       <c r="M64" s="1"/>
@@ -8297,11 +8464,11 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>198.24420000000001</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" ref="S64:S88" si="32">12*R64-Q64-P64-O64-F64</f>
+        <f t="shared" ref="S64:S88" si="33">12*R64-Q64-P64-O64-F64</f>
         <v>774.6174879999993</v>
       </c>
       <c r="T64" s="5">
@@ -8321,7 +8488,7 @@
         <v>11.745000000000001</v>
       </c>
       <c r="X64" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.0926095794984203</v>
       </c>
       <c r="Y64" s="1">
@@ -8363,7 +8530,10 @@
         <f t="shared" si="12"/>
         <v>457</v>
       </c>
-      <c r="AL64" s="1"/>
+      <c r="AL64" s="1">
+        <f t="shared" si="13"/>
+        <v>1209.0463636363636</v>
+      </c>
       <c r="AM64" s="1"/>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
@@ -8406,7 +8576,7 @@
         <v>83.75</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.3499999999999943</v>
       </c>
       <c r="M65" s="1"/>
@@ -8417,15 +8587,15 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.22</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>58.729844000000014</v>
       </c>
       <c r="T65" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>58.729844000000014</v>
       </c>
       <c r="U65" s="5">
@@ -8438,7 +8608,7 @@
         <v>12</v>
       </c>
       <c r="X65" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.5894399535423922</v>
       </c>
       <c r="Y65" s="1">
@@ -8480,7 +8650,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL65" s="1"/>
+      <c r="AL65" s="1">
+        <f t="shared" si="13"/>
+        <v>137.4325272727273</v>
+      </c>
       <c r="AM65" s="1"/>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
@@ -8521,7 +8694,7 @@
         <v>211</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M66" s="1"/>
@@ -8532,15 +8705,15 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>42.2</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>299.40000000000003</v>
       </c>
       <c r="T66" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>299.40000000000003</v>
       </c>
       <c r="U66" s="5">
@@ -8553,7 +8726,7 @@
         <v>12</v>
       </c>
       <c r="X66" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.9052132701421796</v>
       </c>
       <c r="Y66" s="1">
@@ -8595,7 +8768,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL66" s="1"/>
+      <c r="AL66" s="1">
+        <f t="shared" si="13"/>
+        <v>211.4</v>
+      </c>
       <c r="AM66" s="1"/>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
@@ -8638,7 +8814,7 @@
         <v>251</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4</v>
       </c>
       <c r="M67" s="1"/>
@@ -8649,15 +8825,15 @@
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>49.4</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>270.79999999999995</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>270.79999999999995</v>
       </c>
       <c r="U67" s="5">
@@ -8670,7 +8846,7 @@
         <v>12</v>
       </c>
       <c r="X67" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.5182186234817818</v>
       </c>
       <c r="Y67" s="1">
@@ -8712,7 +8888,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL67" s="1"/>
+      <c r="AL67" s="1">
+        <f t="shared" si="13"/>
+        <v>326.2</v>
+      </c>
       <c r="AM67" s="1"/>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
@@ -8755,7 +8934,7 @@
         <v>49.3</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.32200000000000273</v>
       </c>
       <c r="M68" s="1"/>
@@ -8766,15 +8945,15 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.9244000000000003</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>55.891800000000011</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>55.891800000000011</v>
       </c>
       <c r="U68" s="5">
@@ -8787,7 +8966,7 @@
         <v>12</v>
       </c>
       <c r="X68" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.3682439240659381</v>
       </c>
       <c r="Y68" s="1">
@@ -8829,7 +9008,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="1"/>
+      <c r="AL68" s="1">
+        <f t="shared" si="13"/>
+        <v>58.164909090909106</v>
+      </c>
       <c r="AM68" s="1"/>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
@@ -8870,7 +9052,7 @@
         <v>13.1</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-13.1</v>
       </c>
       <c r="M69" s="1"/>
@@ -8881,12 +9063,12 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S69" s="5"/>
       <c r="T69" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U69" s="5">
@@ -8899,7 +9081,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X69" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y69" s="1">
@@ -8943,7 +9125,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="1"/>
+      <c r="AL69" s="1">
+        <f t="shared" si="13"/>
+        <v>1.2233454545454545</v>
+      </c>
       <c r="AM69" s="1"/>
       <c r="AN69" s="1"/>
       <c r="AO69" s="1"/>
@@ -8986,7 +9171,7 @@
         <v>950</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="33">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="34">E70-K70</f>
         <v>-13</v>
       </c>
       <c r="M70" s="1"/>
@@ -8997,15 +9182,15 @@
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1">
-        <f t="shared" ref="R70:R101" si="34">E70/5</f>
+        <f t="shared" ref="R70:R101" si="35">E70/5</f>
         <v>187.4</v>
       </c>
       <c r="S70" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1235.6280000000006</v>
       </c>
       <c r="T70" s="5">
-        <f t="shared" ref="T70:T71" si="35">S70+$T$1*R70</f>
+        <f t="shared" ref="T70:T71" si="36">S70+$T$1*R70</f>
         <v>1187.8410000000006</v>
       </c>
       <c r="U70" s="5">
@@ -9013,7 +9198,7 @@
         <v>438.07576080000024</v>
       </c>
       <c r="V70" s="5">
-        <f t="shared" ref="V70:V71" si="36">T70*$V$1</f>
+        <f t="shared" ref="V70:V71" si="37">T70*$V$1</f>
         <v>749.76523920000034</v>
       </c>
       <c r="W70" s="1">
@@ -9021,7 +9206,7 @@
         <v>11.744999999999999</v>
       </c>
       <c r="X70" s="1">
-        <f t="shared" ref="X70:X101" si="37">(F70+O70+P70+Q70)/R70</f>
+        <f t="shared" ref="X70:X101" si="38">(F70+O70+P70+Q70)/R70</f>
         <v>5.4064674493062936</v>
       </c>
       <c r="Y70" s="1">
@@ -9063,7 +9248,10 @@
         <f t="shared" si="12"/>
         <v>300</v>
       </c>
-      <c r="AL70" s="1"/>
+      <c r="AL70" s="1">
+        <f t="shared" si="13"/>
+        <v>971.72727272727275</v>
+      </c>
       <c r="AM70" s="1"/>
       <c r="AN70" s="1"/>
       <c r="AO70" s="1"/>
@@ -9106,7 +9294,7 @@
         <v>720</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-16</v>
       </c>
       <c r="M71" s="1"/>
@@ -9119,7 +9307,7 @@
       </c>
       <c r="Q71" s="1"/>
       <c r="R71" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>140.80000000000001</v>
       </c>
       <c r="S71" s="5">
@@ -9127,23 +9315,23 @@
         <v>1028.1560000000004</v>
       </c>
       <c r="T71" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>992.25200000000041</v>
       </c>
       <c r="U71" s="5">
-        <f t="shared" ref="U71:U134" si="38">T71-V71</f>
+        <f t="shared" ref="U71:U134" si="39">T71-V71</f>
         <v>365.94253760000015</v>
       </c>
       <c r="V71" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>626.30946240000026</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" ref="W71:W134" si="39">(F71+O71+P71+Q71+T71)/R71</f>
+        <f t="shared" ref="W71:W134" si="40">(F71+O71+P71+Q71+T71)/R71</f>
         <v>7.7450000000000001</v>
       </c>
       <c r="X71" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.69775568181818037</v>
       </c>
       <c r="Y71" s="1">
@@ -9178,14 +9366,17 @@
       </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1">
-        <f t="shared" ref="AJ71:AJ134" si="40">ROUND(G71*U71,0)</f>
+        <f t="shared" ref="AJ71:AJ134" si="41">ROUND(G71*U71,0)</f>
         <v>146</v>
       </c>
       <c r="AK71" s="1">
-        <f t="shared" ref="AK71:AK134" si="41">ROUND(G71*V71,0)</f>
+        <f t="shared" ref="AK71:AK134" si="42">ROUND(G71*V71,0)</f>
         <v>251</v>
       </c>
-      <c r="AL71" s="1"/>
+      <c r="AL71" s="1">
+        <f t="shared" ref="AL71:AL134" si="43">(SUM(Y71:AH71)+R71)/11*7</f>
+        <v>852.34545454545446</v>
+      </c>
       <c r="AM71" s="1"/>
       <c r="AN71" s="1"/>
       <c r="AO71" s="1"/>
@@ -9228,7 +9419,7 @@
         <v>290.75</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13.389999999999986</v>
       </c>
       <c r="M72" s="1"/>
@@ -9239,28 +9430,28 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>60.827999999999996</v>
       </c>
       <c r="S72" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>253.75633399999987</v>
       </c>
       <c r="T72" s="5">
-        <f t="shared" ref="T72:T134" si="42">S72</f>
+        <f t="shared" ref="T72:T134" si="44">S72</f>
         <v>253.75633399999987</v>
       </c>
       <c r="U72" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>253.75633399999987</v>
       </c>
       <c r="V72" s="5"/>
       <c r="W72" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X72" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.8282972644177047</v>
       </c>
       <c r="Y72" s="1">
@@ -9295,14 +9486,17 @@
       </c>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>254</v>
       </c>
       <c r="AK72" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL72" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL72" s="1">
+        <f t="shared" si="43"/>
+        <v>397.80020000000002</v>
+      </c>
       <c r="AM72" s="1"/>
       <c r="AN72" s="1"/>
       <c r="AO72" s="1"/>
@@ -9345,7 +9539,7 @@
         <v>358.5</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>14.625</v>
       </c>
       <c r="M73" s="1"/>
@@ -9356,28 +9550,28 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>74.625</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>292.33090000000004</v>
       </c>
       <c r="T73" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>292.33090000000004</v>
       </c>
       <c r="U73" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>292.33090000000004</v>
       </c>
       <c r="V73" s="5"/>
       <c r="W73" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X73" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8.0826680067001675</v>
       </c>
       <c r="Y73" s="1">
@@ -9412,14 +9606,17 @@
       </c>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>292</v>
       </c>
       <c r="AK73" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL73" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="1">
+        <f t="shared" si="43"/>
+        <v>445.1597818181819</v>
+      </c>
       <c r="AM73" s="1"/>
       <c r="AN73" s="1"/>
       <c r="AO73" s="1"/>
@@ -9462,7 +9659,7 @@
         <v>830</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-33.192999999999984</v>
       </c>
       <c r="M74" s="1"/>
@@ -9473,11 +9670,11 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>159.3614</v>
       </c>
       <c r="S74" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>503.70806800000025</v>
       </c>
       <c r="T74" s="5">
@@ -9485,7 +9682,7 @@
         <v>463.07091100000025</v>
       </c>
       <c r="U74" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>170.7805519768001</v>
       </c>
       <c r="V74" s="5">
@@ -9493,11 +9690,11 @@
         <v>292.29035902320015</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.744999999999999</v>
       </c>
       <c r="X74" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8.8392090681934246</v>
       </c>
       <c r="Y74" s="1">
@@ -9532,14 +9729,17 @@
       </c>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>171</v>
       </c>
       <c r="AK74" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>292</v>
       </c>
-      <c r="AL74" s="1"/>
+      <c r="AL74" s="1">
+        <f t="shared" si="43"/>
+        <v>1149.4308000000001</v>
+      </c>
       <c r="AM74" s="1"/>
       <c r="AN74" s="1"/>
       <c r="AO74" s="1"/>
@@ -9582,7 +9782,7 @@
         <v>240.4</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.2139999999999986</v>
       </c>
       <c r="M75" s="1"/>
@@ -9593,28 +9793,28 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>48.722799999999999</v>
       </c>
       <c r="S75" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>108.03059999999999</v>
       </c>
       <c r="T75" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>108.03059999999999</v>
       </c>
       <c r="U75" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>108.03059999999999</v>
       </c>
       <c r="V75" s="5"/>
       <c r="W75" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X75" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9.7827505808368969</v>
       </c>
       <c r="Y75" s="1">
@@ -9649,14 +9849,17 @@
       </c>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>108</v>
       </c>
       <c r="AK75" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL75" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL75" s="1">
+        <f t="shared" si="43"/>
+        <v>336.21381818181811</v>
+      </c>
       <c r="AM75" s="1"/>
       <c r="AN75" s="1"/>
       <c r="AO75" s="1"/>
@@ -9697,7 +9900,7 @@
         <v>10</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M76" s="1"/>
@@ -9708,7 +9911,7 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="S76" s="5">
@@ -9716,20 +9919,20 @@
         <v>14</v>
       </c>
       <c r="T76" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="U76" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>14</v>
       </c>
       <c r="V76" s="5"/>
       <c r="W76" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10</v>
       </c>
       <c r="X76" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>3</v>
       </c>
       <c r="Y76" s="1">
@@ -9764,14 +9967,17 @@
       </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8</v>
       </c>
       <c r="AK76" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL76" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL76" s="1">
+        <f t="shared" si="43"/>
+        <v>10.563636363636364</v>
+      </c>
       <c r="AM76" s="1"/>
       <c r="AN76" s="1"/>
       <c r="AO76" s="1"/>
@@ -9814,7 +10020,7 @@
         <v>378.45</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-56.676999999999964</v>
       </c>
       <c r="M77" s="1"/>
@@ -9825,28 +10031,28 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>64.354600000000005</v>
       </c>
       <c r="S77" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>288.43760000000009</v>
       </c>
       <c r="T77" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>288.43760000000009</v>
       </c>
       <c r="U77" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>288.43760000000009</v>
       </c>
       <c r="V77" s="5"/>
       <c r="W77" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X77" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.5179956055977328</v>
       </c>
       <c r="Y77" s="1">
@@ -9881,14 +10087,17 @@
       </c>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>288</v>
       </c>
       <c r="AK77" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL77" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="1">
+        <f t="shared" si="43"/>
+        <v>538.68512727272719</v>
+      </c>
       <c r="AM77" s="1"/>
       <c r="AN77" s="1"/>
       <c r="AO77" s="1"/>
@@ -9931,7 +10140,7 @@
         <v>123</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M78" s="1"/>
@@ -9942,28 +10151,28 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>24.6</v>
       </c>
       <c r="S78" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>117.20000000000005</v>
       </c>
       <c r="T78" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>117.20000000000005</v>
       </c>
       <c r="U78" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>117.20000000000005</v>
       </c>
       <c r="V78" s="5"/>
       <c r="W78" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.000000000000002</v>
       </c>
       <c r="X78" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.2357723577235769</v>
       </c>
       <c r="Y78" s="1">
@@ -9998,14 +10207,17 @@
       </c>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>70</v>
       </c>
       <c r="AK78" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL78" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL78" s="1">
+        <f t="shared" si="43"/>
+        <v>152.47272727272724</v>
+      </c>
       <c r="AM78" s="1"/>
       <c r="AN78" s="1"/>
       <c r="AO78" s="1"/>
@@ -10048,7 +10260,7 @@
         <v>30</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="M79" s="1"/>
@@ -10059,28 +10271,28 @@
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
       <c r="R79" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.8</v>
       </c>
       <c r="S79" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>23.599999999999994</v>
       </c>
       <c r="T79" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>23.599999999999994</v>
       </c>
       <c r="U79" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>23.599999999999994</v>
       </c>
       <c r="V79" s="5"/>
       <c r="W79" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X79" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.931034482758621</v>
       </c>
       <c r="Y79" s="1">
@@ -10115,14 +10327,17 @@
       </c>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>14</v>
       </c>
       <c r="AK79" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL79" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL79" s="1">
+        <f t="shared" si="43"/>
+        <v>38.81818181818182</v>
+      </c>
       <c r="AM79" s="1"/>
       <c r="AN79" s="1"/>
       <c r="AO79" s="1"/>
@@ -10165,7 +10380,7 @@
         <v>90</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="M80" s="1"/>
@@ -10176,28 +10391,28 @@
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.8</v>
       </c>
       <c r="S80" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>18.600000000000023</v>
       </c>
       <c r="T80" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>18.600000000000023</v>
       </c>
       <c r="U80" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18.600000000000023</v>
       </c>
       <c r="V80" s="5"/>
       <c r="W80" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X80" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>10.95505617977528</v>
       </c>
       <c r="Y80" s="1">
@@ -10232,14 +10447,17 @@
       </c>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7</v>
       </c>
       <c r="AK80" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL80" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL80" s="1">
+        <f t="shared" si="43"/>
+        <v>145.85454545454547</v>
+      </c>
       <c r="AM80" s="1"/>
       <c r="AN80" s="1"/>
       <c r="AO80" s="1"/>
@@ -10282,7 +10500,7 @@
         <v>132</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-2</v>
       </c>
       <c r="M81" s="1"/>
@@ -10293,28 +10511,28 @@
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>26</v>
       </c>
       <c r="S81" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>102.69999999999999</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>102.69999999999999</v>
       </c>
       <c r="U81" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>102.69999999999999</v>
       </c>
       <c r="V81" s="5"/>
       <c r="W81" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X81" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8.0500000000000007</v>
       </c>
       <c r="Y81" s="1">
@@ -10349,14 +10567,17 @@
       </c>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>34</v>
       </c>
       <c r="AK81" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL81" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="1">
+        <f t="shared" si="43"/>
+        <v>173.85454545454547</v>
+      </c>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1"/>
       <c r="AO81" s="1"/>
@@ -10399,7 +10620,7 @@
         <v>103</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M82" s="1"/>
@@ -10410,28 +10631,28 @@
       <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>20.6</v>
       </c>
       <c r="S82" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>125.00000000000003</v>
       </c>
       <c r="T82" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>125.00000000000003</v>
       </c>
       <c r="U82" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>125.00000000000003</v>
       </c>
       <c r="V82" s="5"/>
       <c r="W82" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X82" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>5.932038834951455</v>
       </c>
       <c r="Y82" s="1">
@@ -10466,14 +10687,17 @@
       </c>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>44</v>
       </c>
       <c r="AK82" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL82" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL82" s="1">
+        <f t="shared" si="43"/>
+        <v>91.63636363636364</v>
+      </c>
       <c r="AM82" s="1"/>
       <c r="AN82" s="1"/>
       <c r="AO82" s="1"/>
@@ -10516,7 +10740,7 @@
         <v>451</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-5</v>
       </c>
       <c r="M83" s="1"/>
@@ -10527,19 +10751,19 @@
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>89.2</v>
       </c>
       <c r="S83" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>363.40000000000009</v>
       </c>
       <c r="T83" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>363.40000000000009</v>
       </c>
       <c r="U83" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>134.02192000000005</v>
       </c>
       <c r="V83" s="5">
@@ -10547,11 +10771,11 @@
         <v>229.37808000000004</v>
       </c>
       <c r="W83" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X83" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.9260089686098656</v>
       </c>
       <c r="Y83" s="1">
@@ -10586,14 +10810,17 @@
       </c>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>50</v>
       </c>
       <c r="AK83" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>85</v>
       </c>
-      <c r="AL83" s="1"/>
+      <c r="AL83" s="1">
+        <f t="shared" si="43"/>
+        <v>743.78181818181815</v>
+      </c>
       <c r="AM83" s="1"/>
       <c r="AN83" s="1"/>
       <c r="AO83" s="1"/>
@@ -10636,7 +10863,7 @@
         <v>115</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M84" s="1"/>
@@ -10647,28 +10874,28 @@
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>23</v>
       </c>
       <c r="S84" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>117.60000000000008</v>
       </c>
       <c r="T84" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>117.60000000000008</v>
       </c>
       <c r="U84" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>117.60000000000008</v>
       </c>
       <c r="V84" s="5"/>
       <c r="W84" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X84" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6.8869565217391271</v>
       </c>
       <c r="Y84" s="1">
@@ -10703,14 +10930,17 @@
       </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>71</v>
       </c>
       <c r="AK84" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL84" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL84" s="1">
+        <f t="shared" si="43"/>
+        <v>162.14545454545456</v>
+      </c>
       <c r="AM84" s="1"/>
       <c r="AN84" s="1"/>
       <c r="AO84" s="1"/>
@@ -10753,7 +10983,7 @@
         <v>46</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-3</v>
       </c>
       <c r="M85" s="1"/>
@@ -10764,7 +10994,7 @@
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8.6</v>
       </c>
       <c r="S85" s="5">
@@ -10772,20 +11002,20 @@
         <v>56.599999999999994</v>
       </c>
       <c r="T85" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>56.599999999999994</v>
       </c>
       <c r="U85" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>56.599999999999994</v>
       </c>
       <c r="V85" s="5"/>
       <c r="W85" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11</v>
       </c>
       <c r="X85" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.4186046511627906</v>
       </c>
       <c r="Y85" s="1">
@@ -10820,14 +11050,17 @@
       </c>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>19</v>
       </c>
       <c r="AK85" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL85" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL85" s="1">
+        <f t="shared" si="43"/>
+        <v>49.636363636363633</v>
+      </c>
       <c r="AM85" s="1"/>
       <c r="AN85" s="1"/>
       <c r="AO85" s="1"/>
@@ -10870,7 +11103,7 @@
         <v>278</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="M86" s="1"/>
@@ -10881,19 +11114,19 @@
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>55.4</v>
       </c>
       <c r="S86" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>373.87400000000014</v>
       </c>
       <c r="T86" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>373.87400000000014</v>
       </c>
       <c r="U86" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>137.88473120000006</v>
       </c>
       <c r="V86" s="5">
@@ -10901,11 +11134,11 @@
         <v>235.98926880000008</v>
       </c>
       <c r="W86" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X86" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>5.2513718411552324</v>
       </c>
       <c r="Y86" s="1">
@@ -10940,14 +11173,17 @@
       </c>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>55</v>
       </c>
       <c r="AK86" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>94</v>
       </c>
-      <c r="AL86" s="1"/>
+      <c r="AL86" s="1">
+        <f t="shared" si="43"/>
+        <v>354.83636363636367</v>
+      </c>
       <c r="AM86" s="1"/>
       <c r="AN86" s="1"/>
       <c r="AO86" s="1"/>
@@ -10988,7 +11224,7 @@
         <v>176</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-55</v>
       </c>
       <c r="M87" s="1"/>
@@ -10999,7 +11235,7 @@
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>24.2</v>
       </c>
       <c r="S87" s="5">
@@ -11007,20 +11243,20 @@
         <v>171</v>
       </c>
       <c r="T87" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>171</v>
       </c>
       <c r="U87" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>171</v>
       </c>
       <c r="V87" s="5"/>
       <c r="W87" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10</v>
       </c>
       <c r="X87" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2.9338842975206614</v>
       </c>
       <c r="Y87" s="1">
@@ -11055,14 +11291,17 @@
       </c>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>60</v>
       </c>
       <c r="AK87" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL87" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL87" s="1">
+        <f t="shared" si="43"/>
+        <v>127.14545454545453</v>
+      </c>
       <c r="AM87" s="1"/>
       <c r="AN87" s="1"/>
       <c r="AO87" s="1"/>
@@ -11105,7 +11344,7 @@
         <v>228</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-8</v>
       </c>
       <c r="M88" s="1"/>
@@ -11118,28 +11357,28 @@
       </c>
       <c r="Q88" s="1"/>
       <c r="R88" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>44</v>
       </c>
       <c r="S88" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>264</v>
       </c>
       <c r="T88" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>264</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>264</v>
       </c>
       <c r="V88" s="5"/>
       <c r="W88" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X88" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6</v>
       </c>
       <c r="Y88" s="1">
@@ -11174,14 +11413,17 @@
       </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>92</v>
       </c>
       <c r="AK88" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL88" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL88" s="1">
+        <f t="shared" si="43"/>
+        <v>329.89090909090913</v>
+      </c>
       <c r="AM88" s="1"/>
       <c r="AN88" s="1"/>
       <c r="AO88" s="1"/>
@@ -11224,7 +11466,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-11</v>
       </c>
       <c r="M89" s="1"/>
@@ -11235,25 +11477,25 @@
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>28</v>
       </c>
       <c r="S89" s="5"/>
       <c r="T89" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U89" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V89" s="5"/>
       <c r="W89" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.924999999999999</v>
       </c>
       <c r="X89" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.924999999999999</v>
       </c>
       <c r="Y89" s="1">
@@ -11288,14 +11530,17 @@
       </c>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK89" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL89" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL89" s="1">
+        <f t="shared" si="43"/>
+        <v>139.87272727272727</v>
+      </c>
       <c r="AM89" s="1"/>
       <c r="AN89" s="1"/>
       <c r="AO89" s="1"/>
@@ -11338,7 +11583,7 @@
         <v>27.9</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-19.795999999999999</v>
       </c>
       <c r="M90" s="1"/>
@@ -11349,27 +11594,27 @@
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.6207999999999998</v>
       </c>
       <c r="S90" s="5">
         <v>20</v>
       </c>
       <c r="T90" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>20</v>
       </c>
       <c r="U90" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>20</v>
       </c>
       <c r="V90" s="5"/>
       <c r="W90" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>24.261475814412638</v>
       </c>
       <c r="X90" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.92189042448174</v>
       </c>
       <c r="Y90" s="1">
@@ -11404,14 +11649,17 @@
       </c>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>20</v>
       </c>
       <c r="AK90" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL90" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL90" s="1">
+        <f t="shared" si="43"/>
+        <v>45.45647272727274</v>
+      </c>
       <c r="AM90" s="1"/>
       <c r="AN90" s="1"/>
       <c r="AO90" s="1"/>
@@ -11454,7 +11702,7 @@
         <v>34</v>
       </c>
       <c r="L91" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-14</v>
       </c>
       <c r="M91" s="10"/>
@@ -11465,25 +11713,25 @@
       <c r="P91" s="10"/>
       <c r="Q91" s="10"/>
       <c r="R91" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4</v>
       </c>
       <c r="S91" s="12"/>
       <c r="T91" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U91" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V91" s="5"/>
       <c r="W91" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6.5</v>
       </c>
       <c r="X91" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6.5</v>
       </c>
       <c r="Y91" s="10">
@@ -11518,14 +11766,17 @@
       </c>
       <c r="AI91" s="10"/>
       <c r="AJ91" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK91" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL91" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="1">
+        <f t="shared" si="43"/>
+        <v>19.09090909090909</v>
+      </c>
       <c r="AM91" s="1"/>
       <c r="AN91" s="1"/>
       <c r="AO91" s="1"/>
@@ -11568,7 +11819,7 @@
         <v>154.1</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.8100000000000023</v>
       </c>
       <c r="M92" s="1"/>
@@ -11579,25 +11830,25 @@
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>31.181999999999999</v>
       </c>
       <c r="S92" s="5"/>
       <c r="T92" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U92" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V92" s="5"/>
       <c r="W92" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.484093387210571</v>
       </c>
       <c r="X92" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>15.484093387210571</v>
       </c>
       <c r="Y92" s="1">
@@ -11632,14 +11883,17 @@
       </c>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK92" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL92" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL92" s="1">
+        <f t="shared" si="43"/>
+        <v>297.67780000000005</v>
+      </c>
       <c r="AM92" s="1"/>
       <c r="AN92" s="1"/>
       <c r="AO92" s="1"/>
@@ -11682,7 +11936,7 @@
         <v>924.82500000000005</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-12.990000000000009</v>
       </c>
       <c r="M93" s="1"/>
@@ -11693,11 +11947,11 @@
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>182.36700000000002</v>
       </c>
       <c r="S93" s="5">
-        <f t="shared" ref="S93" si="43">12*R93-Q93-P93-O93-F93</f>
+        <f t="shared" ref="S93" si="45">12*R93-Q93-P93-O93-F93</f>
         <v>881.87341400000048</v>
       </c>
       <c r="T93" s="5">
@@ -11705,7 +11959,7 @@
         <v>835.36982900000044</v>
       </c>
       <c r="U93" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>308.08439293520019</v>
       </c>
       <c r="V93" s="5">
@@ -11713,11 +11967,11 @@
         <v>527.28543606480025</v>
       </c>
       <c r="W93" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.744999999999999</v>
       </c>
       <c r="X93" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.1642928051675998</v>
       </c>
       <c r="Y93" s="1">
@@ -11752,14 +12006,17 @@
       </c>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>308</v>
       </c>
       <c r="AK93" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>527</v>
       </c>
-      <c r="AL93" s="1"/>
+      <c r="AL93" s="1">
+        <f t="shared" si="43"/>
+        <v>1274.6492181818182</v>
+      </c>
       <c r="AM93" s="1"/>
       <c r="AN93" s="1"/>
       <c r="AO93" s="1"/>
@@ -11790,7 +12047,7 @@
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M94" s="10"/>
@@ -11801,25 +12058,25 @@
       <c r="P94" s="10"/>
       <c r="Q94" s="10"/>
       <c r="R94" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S94" s="12"/>
       <c r="T94" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U94" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V94" s="5"/>
       <c r="W94" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X94" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y94" s="10">
@@ -11856,14 +12113,17 @@
         <v>43</v>
       </c>
       <c r="AJ94" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK94" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL94" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL94" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM94" s="1"/>
       <c r="AN94" s="1"/>
       <c r="AO94" s="1"/>
@@ -11906,7 +12166,7 @@
         <v>2235.35</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-55.284000000000106</v>
       </c>
       <c r="M95" s="1"/>
@@ -11917,11 +12177,11 @@
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
       <c r="R95" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>436.01319999999998</v>
       </c>
       <c r="S95" s="5">
-        <f t="shared" ref="S95" si="44">12*R95-Q95-P95-O95-F95</f>
+        <f t="shared" ref="S95" si="46">12*R95-Q95-P95-O95-F95</f>
         <v>1766.4551256000013</v>
       </c>
       <c r="T95" s="5">
@@ -11929,7 +12189,7 @@
         <v>1655.2717596000014</v>
       </c>
       <c r="U95" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>610.46422494048056</v>
       </c>
       <c r="V95" s="5">
@@ -11937,11 +12197,11 @@
         <v>1044.8075346595208</v>
       </c>
       <c r="W95" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.745000000000001</v>
       </c>
       <c r="X95" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7.9486200748050715</v>
       </c>
       <c r="Y95" s="1">
@@ -11976,14 +12236,17 @@
       </c>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>610</v>
       </c>
       <c r="AK95" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1045</v>
       </c>
-      <c r="AL95" s="1"/>
+      <c r="AL95" s="1">
+        <f t="shared" si="43"/>
+        <v>2874.4157272727275</v>
+      </c>
       <c r="AM95" s="1"/>
       <c r="AN95" s="1"/>
       <c r="AO95" s="1"/>
@@ -12026,7 +12289,7 @@
         <v>2742.2</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-92.086999999999989</v>
       </c>
       <c r="M96" s="1"/>
@@ -12039,25 +12302,25 @@
         <v>2900</v>
       </c>
       <c r="R96" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>530.02260000000001</v>
       </c>
       <c r="S96" s="5"/>
       <c r="T96" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U96" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V96" s="5"/>
       <c r="W96" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>13.260860951966952</v>
       </c>
       <c r="X96" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>13.260860951966952</v>
       </c>
       <c r="Y96" s="1">
@@ -12092,14 +12355,17 @@
       </c>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK96" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL96" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL96" s="1">
+        <f t="shared" si="43"/>
+        <v>3601.8055818181815</v>
+      </c>
       <c r="AM96" s="1"/>
       <c r="AN96" s="1"/>
       <c r="AO96" s="1"/>
@@ -12142,7 +12408,7 @@
         <v>3003.4</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-72.602000000000317</v>
       </c>
       <c r="M97" s="1"/>
@@ -12155,25 +12421,25 @@
         <v>1400</v>
       </c>
       <c r="R97" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>586.15959999999995</v>
       </c>
       <c r="S97" s="5"/>
       <c r="T97" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U97" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V97" s="5"/>
       <c r="W97" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.647799336562944</v>
       </c>
       <c r="X97" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>12.647799336562944</v>
       </c>
       <c r="Y97" s="1">
@@ -12208,14 +12474,17 @@
       </c>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK97" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL97" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL97" s="1">
+        <f t="shared" si="43"/>
+        <v>4078.489418181819</v>
+      </c>
       <c r="AM97" s="1"/>
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
@@ -12258,7 +12527,7 @@
         <v>31.5</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5.0230000000000032</v>
       </c>
       <c r="M98" s="1"/>
@@ -12269,25 +12538,25 @@
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.3046000000000006</v>
       </c>
       <c r="S98" s="5"/>
       <c r="T98" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U98" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V98" s="5"/>
       <c r="W98" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>24.653369109875968</v>
       </c>
       <c r="X98" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>24.653369109875968</v>
       </c>
       <c r="Y98" s="1">
@@ -12324,14 +12593,17 @@
         <v>86</v>
       </c>
       <c r="AJ98" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK98" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL98" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL98" s="1">
+        <f t="shared" si="43"/>
+        <v>58.227018181818174</v>
+      </c>
       <c r="AM98" s="1"/>
       <c r="AN98" s="1"/>
       <c r="AO98" s="1"/>
@@ -12374,7 +12646,7 @@
         <v>13.2</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-1.3449999999999989</v>
       </c>
       <c r="M99" s="10"/>
@@ -12385,25 +12657,25 @@
       <c r="P99" s="10"/>
       <c r="Q99" s="10"/>
       <c r="R99" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.371</v>
       </c>
       <c r="S99" s="12"/>
       <c r="T99" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U99" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V99" s="5"/>
       <c r="W99" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>13.736398144242937</v>
       </c>
       <c r="X99" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>13.736398144242937</v>
       </c>
       <c r="Y99" s="10">
@@ -12440,14 +12712,17 @@
         <v>73</v>
       </c>
       <c r="AJ99" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK99" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL99" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL99" s="1">
+        <f t="shared" si="43"/>
+        <v>29.322236363636364</v>
+      </c>
       <c r="AM99" s="1"/>
       <c r="AN99" s="1"/>
       <c r="AO99" s="1"/>
@@ -12486,7 +12761,7 @@
         <v>9.1</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.35400000000000098</v>
       </c>
       <c r="M100" s="10"/>
@@ -12497,25 +12772,25 @@
       <c r="P100" s="10"/>
       <c r="Q100" s="10"/>
       <c r="R100" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.8908</v>
       </c>
       <c r="S100" s="12"/>
       <c r="T100" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U100" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V100" s="5"/>
       <c r="W100" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>198.88883012481492</v>
       </c>
       <c r="X100" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>198.88883012481492</v>
       </c>
       <c r="Y100" s="10">
@@ -12552,14 +12827,17 @@
         <v>183</v>
       </c>
       <c r="AJ100" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK100" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL100" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL100" s="1">
+        <f t="shared" si="43"/>
+        <v>6.5553090909090903</v>
+      </c>
       <c r="AM100" s="1"/>
       <c r="AN100" s="1"/>
       <c r="AO100" s="1"/>
@@ -12602,7 +12880,7 @@
         <v>367</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-13</v>
       </c>
       <c r="M101" s="1"/>
@@ -12613,31 +12891,31 @@
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.8</v>
       </c>
       <c r="S101" s="5">
-        <f t="shared" ref="S101" si="45">12*R101-Q101-P101-O101-F101</f>
+        <f t="shared" ref="S101" si="47">12*R101-Q101-P101-O101-F101</f>
         <v>483.58800000000019</v>
       </c>
       <c r="T101" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>483.58800000000019</v>
       </c>
       <c r="U101" s="5">
+        <f t="shared" si="39"/>
+        <v>178.34725440000005</v>
+      </c>
+      <c r="V101" s="5">
+        <f t="shared" ref="V101:V102" si="48">T101*$V$1</f>
+        <v>305.24074560000014</v>
+      </c>
+      <c r="W101" s="1">
+        <f t="shared" si="40"/>
+        <v>12</v>
+      </c>
+      <c r="X101" s="1">
         <f t="shared" si="38"/>
-        <v>178.34725440000005</v>
-      </c>
-      <c r="V101" s="5">
-        <f t="shared" ref="V101:V102" si="46">T101*$V$1</f>
-        <v>305.24074560000014</v>
-      </c>
-      <c r="W101" s="1">
-        <f t="shared" si="39"/>
-        <v>12</v>
-      </c>
-      <c r="X101" s="1">
-        <f t="shared" si="37"/>
         <v>5.1696610169491493</v>
       </c>
       <c r="Y101" s="1">
@@ -12672,14 +12950,17 @@
       </c>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>54</v>
       </c>
       <c r="AK101" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>92</v>
       </c>
-      <c r="AL101" s="1"/>
+      <c r="AL101" s="1">
+        <f t="shared" si="43"/>
+        <v>291.2</v>
+      </c>
       <c r="AM101" s="1"/>
       <c r="AN101" s="1"/>
       <c r="AO101" s="1"/>
@@ -12723,7 +13004,7 @@
         <v>250</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="47">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="49">E102-K102</f>
         <v>-18</v>
       </c>
       <c r="M102" s="1"/>
@@ -12736,7 +13017,7 @@
       </c>
       <c r="Q102" s="1"/>
       <c r="R102" s="1">
-        <f t="shared" ref="R102:R133" si="48">E102/5</f>
+        <f t="shared" ref="R102:R133" si="50">E102/5</f>
         <v>46.4</v>
       </c>
       <c r="S102" s="5">
@@ -12744,23 +13025,23 @@
         <v>321.7</v>
       </c>
       <c r="T102" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>321.7</v>
       </c>
       <c r="U102" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>118.64295999999999</v>
       </c>
       <c r="V102" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>203.05704</v>
       </c>
       <c r="W102" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11</v>
       </c>
       <c r="X102" s="1">
-        <f t="shared" ref="X102:X133" si="49">(F102+O102+P102+Q102)/R102</f>
+        <f t="shared" ref="X102:X133" si="51">(F102+O102+P102+Q102)/R102</f>
         <v>4.0668103448275863</v>
       </c>
       <c r="Y102" s="1">
@@ -12795,14 +13076,17 @@
       </c>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>36</v>
       </c>
       <c r="AK102" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>61</v>
       </c>
-      <c r="AL102" s="1"/>
+      <c r="AL102" s="1">
+        <f t="shared" si="43"/>
+        <v>210.38181818181815</v>
+      </c>
       <c r="AM102" s="1"/>
       <c r="AN102" s="1"/>
       <c r="AO102" s="1"/>
@@ -12845,7 +13129,7 @@
         <v>93</v>
       </c>
       <c r="L103" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1</v>
       </c>
       <c r="M103" s="10"/>
@@ -12856,25 +13140,25 @@
       <c r="P103" s="10"/>
       <c r="Q103" s="10"/>
       <c r="R103" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>18.399999999999999</v>
       </c>
       <c r="S103" s="12"/>
       <c r="T103" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U103" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V103" s="5"/>
       <c r="W103" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.48913043478260876</v>
       </c>
       <c r="X103" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.48913043478260876</v>
       </c>
       <c r="Y103" s="10">
@@ -12909,14 +13193,17 @@
       </c>
       <c r="AI103" s="10"/>
       <c r="AJ103" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK103" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL103" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL103" s="1">
+        <f t="shared" si="43"/>
+        <v>63.763636363636351</v>
+      </c>
       <c r="AM103" s="1"/>
       <c r="AN103" s="1"/>
       <c r="AO103" s="1"/>
@@ -12947,7 +13234,7 @@
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
       <c r="L104" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M104" s="10"/>
@@ -12958,25 +13245,25 @@
       <c r="P104" s="10"/>
       <c r="Q104" s="10"/>
       <c r="R104" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S104" s="12"/>
       <c r="T104" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U104" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V104" s="5"/>
       <c r="W104" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X104" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y104" s="10">
@@ -13013,14 +13300,17 @@
         <v>43</v>
       </c>
       <c r="AJ104" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK104" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL104" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL104" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM104" s="1"/>
       <c r="AN104" s="1"/>
       <c r="AO104" s="1"/>
@@ -13063,7 +13353,7 @@
         <v>177</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-85</v>
       </c>
       <c r="M105" s="1"/>
@@ -13074,25 +13364,25 @@
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>18.399999999999999</v>
       </c>
       <c r="S105" s="5"/>
       <c r="T105" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V105" s="5"/>
       <c r="W105" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18.54347826086957</v>
       </c>
       <c r="X105" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>18.54347826086957</v>
       </c>
       <c r="Y105" s="1">
@@ -13127,14 +13417,17 @@
       </c>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK105" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL105" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL105" s="1">
+        <f t="shared" si="43"/>
+        <v>228.83636363636361</v>
+      </c>
       <c r="AM105" s="1"/>
       <c r="AN105" s="1"/>
       <c r="AO105" s="1"/>
@@ -13177,7 +13470,7 @@
         <v>139</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-6</v>
       </c>
       <c r="M106" s="1"/>
@@ -13188,28 +13481,28 @@
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>26.6</v>
       </c>
       <c r="S106" s="5">
-        <f t="shared" ref="S106" si="50">12*R106-Q106-P106-O106-F106</f>
+        <f t="shared" ref="S106" si="52">12*R106-Q106-P106-O106-F106</f>
         <v>104.61200000000002</v>
       </c>
       <c r="T106" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>104.61200000000002</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>104.61200000000002</v>
       </c>
       <c r="V106" s="5"/>
       <c r="W106" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.000000000000002</v>
       </c>
       <c r="X106" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>8.0672180451127815</v>
       </c>
       <c r="Y106" s="1">
@@ -13244,14 +13537,17 @@
       </c>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7</v>
       </c>
       <c r="AK106" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL106" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="1">
+        <f t="shared" si="43"/>
+        <v>174.23636363636365</v>
+      </c>
       <c r="AM106" s="1"/>
       <c r="AN106" s="1"/>
       <c r="AO106" s="1"/>
@@ -13294,7 +13590,7 @@
         <v>93</v>
       </c>
       <c r="L107" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-9</v>
       </c>
       <c r="M107" s="10"/>
@@ -13305,25 +13601,25 @@
       <c r="P107" s="10"/>
       <c r="Q107" s="10"/>
       <c r="R107" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>16.8</v>
       </c>
       <c r="S107" s="12"/>
       <c r="T107" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V107" s="5"/>
       <c r="W107" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10</v>
       </c>
       <c r="X107" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10</v>
       </c>
       <c r="Y107" s="10">
@@ -13358,14 +13654,17 @@
       </c>
       <c r="AI107" s="10"/>
       <c r="AJ107" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK107" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL107" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL107" s="1">
+        <f t="shared" si="43"/>
+        <v>125.99999999999997</v>
+      </c>
       <c r="AM107" s="1"/>
       <c r="AN107" s="1"/>
       <c r="AO107" s="1"/>
@@ -13402,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="L108" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-7</v>
       </c>
       <c r="M108" s="10"/>
@@ -13413,25 +13712,25 @@
       <c r="P108" s="10"/>
       <c r="Q108" s="10"/>
       <c r="R108" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S108" s="12"/>
       <c r="T108" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V108" s="5"/>
       <c r="W108" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X108" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y108" s="10">
@@ -13466,14 +13765,17 @@
       </c>
       <c r="AI108" s="10"/>
       <c r="AJ108" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK108" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL108" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="1">
+        <f t="shared" si="43"/>
+        <v>37.036363636363639</v>
+      </c>
       <c r="AM108" s="1"/>
       <c r="AN108" s="1"/>
       <c r="AO108" s="1"/>
@@ -13514,7 +13816,7 @@
         <v>41</v>
       </c>
       <c r="L109" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-40</v>
       </c>
       <c r="M109" s="10"/>
@@ -13525,25 +13827,25 @@
       <c r="P109" s="10"/>
       <c r="Q109" s="10"/>
       <c r="R109" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.2</v>
       </c>
       <c r="S109" s="12"/>
       <c r="T109" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V109" s="5"/>
       <c r="W109" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>20</v>
       </c>
       <c r="X109" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>20</v>
       </c>
       <c r="Y109" s="10">
@@ -13578,14 +13880,17 @@
       </c>
       <c r="AI109" s="10"/>
       <c r="AJ109" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK109" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL109" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="1">
+        <f t="shared" si="43"/>
+        <v>69.109090909090909</v>
+      </c>
       <c r="AM109" s="1"/>
       <c r="AN109" s="1"/>
       <c r="AO109" s="1"/>
@@ -13626,7 +13931,7 @@
         <v>2</v>
       </c>
       <c r="L110" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M110" s="10"/>
@@ -13637,25 +13942,25 @@
       <c r="P110" s="10"/>
       <c r="Q110" s="10"/>
       <c r="R110" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.4</v>
       </c>
       <c r="S110" s="12"/>
       <c r="T110" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U110" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V110" s="5"/>
       <c r="W110" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>67.5</v>
       </c>
       <c r="X110" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>67.5</v>
       </c>
       <c r="Y110" s="10">
@@ -13692,14 +13997,17 @@
         <v>86</v>
       </c>
       <c r="AJ110" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK110" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL110" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL110" s="1">
+        <f t="shared" si="43"/>
+        <v>7.1272727272727279</v>
+      </c>
       <c r="AM110" s="1"/>
       <c r="AN110" s="1"/>
       <c r="AO110" s="1"/>
@@ -13742,7 +14050,7 @@
         <v>232</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-5</v>
       </c>
       <c r="M111" s="1"/>
@@ -13755,7 +14063,7 @@
       </c>
       <c r="Q111" s="1"/>
       <c r="R111" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>45.4</v>
       </c>
       <c r="S111" s="5">
@@ -13763,11 +14071,11 @@
         <v>330.4</v>
       </c>
       <c r="T111" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>330.4</v>
       </c>
       <c r="U111" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>121.85151999999999</v>
       </c>
       <c r="V111" s="5">
@@ -13775,11 +14083,11 @@
         <v>208.54847999999998</v>
       </c>
       <c r="W111" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11</v>
       </c>
       <c r="X111" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>3.7224669603524232</v>
       </c>
       <c r="Y111" s="1">
@@ -13814,14 +14122,17 @@
       </c>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>37</v>
       </c>
       <c r="AK111" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>63</v>
       </c>
-      <c r="AL111" s="1"/>
+      <c r="AL111" s="1">
+        <f t="shared" si="43"/>
+        <v>234.18181818181819</v>
+      </c>
       <c r="AM111" s="1"/>
       <c r="AN111" s="1"/>
       <c r="AO111" s="1"/>
@@ -13864,7 +14175,7 @@
         <v>90.95</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>12.075000000000003</v>
       </c>
       <c r="M112" s="1"/>
@@ -13875,28 +14186,28 @@
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>20.605</v>
       </c>
       <c r="S112" s="5">
-        <f t="shared" ref="S112" si="51">12*R112-Q112-P112-O112-F112</f>
+        <f t="shared" ref="S112" si="53">12*R112-Q112-P112-O112-F112</f>
         <v>55.491199999999992</v>
       </c>
       <c r="T112" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>55.491199999999992</v>
       </c>
       <c r="U112" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>55.491199999999992</v>
       </c>
       <c r="V112" s="5"/>
       <c r="W112" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X112" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.306906090754671</v>
       </c>
       <c r="Y112" s="1">
@@ -13931,14 +14242,17 @@
       </c>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>55</v>
       </c>
       <c r="AK112" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL112" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL112" s="1">
+        <f t="shared" si="43"/>
+        <v>142.39400000000001</v>
+      </c>
       <c r="AM112" s="1"/>
       <c r="AN112" s="1"/>
       <c r="AO112" s="1"/>
@@ -13969,7 +14283,7 @@
       <c r="J113" s="10"/>
       <c r="K113" s="10"/>
       <c r="L113" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M113" s="10"/>
@@ -13980,25 +14294,25 @@
       <c r="P113" s="10"/>
       <c r="Q113" s="10"/>
       <c r="R113" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S113" s="12"/>
       <c r="T113" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U113" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V113" s="5"/>
       <c r="W113" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X113" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y113" s="10">
@@ -14035,14 +14349,17 @@
         <v>43</v>
       </c>
       <c r="AJ113" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK113" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL113" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL113" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM113" s="1"/>
       <c r="AN113" s="1"/>
       <c r="AO113" s="1"/>
@@ -14085,7 +14402,7 @@
         <v>10</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1</v>
       </c>
       <c r="M114" s="1"/>
@@ -14096,25 +14413,25 @@
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
       <c r="R114" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1.8</v>
       </c>
       <c r="S114" s="5"/>
       <c r="T114" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U114" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V114" s="5"/>
       <c r="W114" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.666666666666666</v>
       </c>
       <c r="X114" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.666666666666666</v>
       </c>
       <c r="Y114" s="1">
@@ -14149,14 +14466,17 @@
       </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK114" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL114" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL114" s="1">
+        <f t="shared" si="43"/>
+        <v>12.345454545454547</v>
+      </c>
       <c r="AM114" s="1"/>
       <c r="AN114" s="1"/>
       <c r="AO114" s="1"/>
@@ -14199,7 +14519,7 @@
         <v>231</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-15</v>
       </c>
       <c r="M115" s="1"/>
@@ -14210,28 +14530,28 @@
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>43.2</v>
       </c>
       <c r="S115" s="5">
-        <f t="shared" ref="S115:S120" si="52">12*R115-Q115-P115-O115-F115</f>
+        <f t="shared" ref="S115:S120" si="54">12*R115-Q115-P115-O115-F115</f>
         <v>216.26800000000003</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>216.26800000000003</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>216.26800000000003</v>
       </c>
       <c r="V115" s="5"/>
       <c r="W115" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.000000000000002</v>
       </c>
       <c r="X115" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>6.9937962962962974</v>
       </c>
       <c r="Y115" s="1">
@@ -14266,14 +14586,17 @@
       </c>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>17</v>
       </c>
       <c r="AK115" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL115" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL115" s="1">
+        <f t="shared" si="43"/>
+        <v>305.83636363636361</v>
+      </c>
       <c r="AM115" s="1"/>
       <c r="AN115" s="1"/>
       <c r="AO115" s="1"/>
@@ -14316,7 +14639,7 @@
         <v>179</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-13</v>
       </c>
       <c r="M116" s="1"/>
@@ -14327,7 +14650,7 @@
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>33.200000000000003</v>
       </c>
       <c r="S116" s="5">
@@ -14335,20 +14658,20 @@
         <v>231.364</v>
       </c>
       <c r="T116" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>231.364</v>
       </c>
       <c r="U116" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>231.364</v>
       </c>
       <c r="V116" s="5"/>
       <c r="W116" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>9</v>
       </c>
       <c r="X116" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2.0312048192771086</v>
       </c>
       <c r="Y116" s="1">
@@ -14383,14 +14706,17 @@
       </c>
       <c r="AI116" s="1"/>
       <c r="AJ116" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>19</v>
       </c>
       <c r="AK116" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL116" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL116" s="1">
+        <f t="shared" si="43"/>
+        <v>215.72727272727269</v>
+      </c>
       <c r="AM116" s="1"/>
       <c r="AN116" s="1"/>
       <c r="AO116" s="1"/>
@@ -14433,7 +14759,7 @@
         <v>4</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-2</v>
       </c>
       <c r="M117" s="1"/>
@@ -14444,25 +14770,25 @@
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.4</v>
       </c>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U117" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V117" s="5"/>
       <c r="W117" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>62.5</v>
       </c>
       <c r="X117" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>62.5</v>
       </c>
       <c r="Y117" s="1">
@@ -14499,14 +14825,17 @@
         <v>184</v>
       </c>
       <c r="AJ117" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK117" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL117" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL117" s="1">
+        <f t="shared" si="43"/>
+        <v>8.2727272727272734</v>
+      </c>
       <c r="AM117" s="1"/>
       <c r="AN117" s="1"/>
       <c r="AO117" s="1"/>
@@ -14549,7 +14878,7 @@
         <v>451.8</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-24.040999999999997</v>
       </c>
       <c r="M118" s="1"/>
@@ -14560,28 +14889,28 @@
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>85.5518</v>
       </c>
       <c r="S118" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>253.30019399999969</v>
       </c>
       <c r="T118" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>253.30019399999969</v>
       </c>
       <c r="U118" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>253.30019399999969</v>
       </c>
       <c r="V118" s="5"/>
       <c r="W118" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X118" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.039218415042118</v>
       </c>
       <c r="Y118" s="1">
@@ -14616,14 +14945,17 @@
       </c>
       <c r="AI118" s="1"/>
       <c r="AJ118" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>253</v>
       </c>
       <c r="AK118" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL118" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL118" s="1">
+        <f t="shared" si="43"/>
+        <v>508.3299454545454</v>
+      </c>
       <c r="AM118" s="1"/>
       <c r="AN118" s="1"/>
       <c r="AO118" s="1"/>
@@ -14666,7 +14998,7 @@
         <v>295.5</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-3.7479999999999905</v>
       </c>
       <c r="M119" s="1"/>
@@ -14677,28 +15009,28 @@
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
       <c r="R119" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>58.3504</v>
       </c>
       <c r="S119" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>166.52969999999996</v>
       </c>
       <c r="T119" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>166.52969999999996</v>
       </c>
       <c r="U119" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>166.52969999999996</v>
       </c>
       <c r="V119" s="5"/>
       <c r="W119" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X119" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.146040129973402</v>
       </c>
       <c r="Y119" s="1">
@@ -14733,14 +15065,17 @@
       </c>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>167</v>
       </c>
       <c r="AK119" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL119" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL119" s="1">
+        <f t="shared" si="43"/>
+        <v>300.36439999999999</v>
+      </c>
       <c r="AM119" s="1"/>
       <c r="AN119" s="1"/>
       <c r="AO119" s="1"/>
@@ -14784,7 +15119,7 @@
         <v>520.25</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-54.269000000000005</v>
       </c>
       <c r="M120" s="1"/>
@@ -14795,28 +15130,28 @@
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>93.196200000000005</v>
       </c>
       <c r="S120" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>230.14787400000012</v>
       </c>
       <c r="T120" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>230.14787400000012</v>
       </c>
       <c r="U120" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>230.14787400000012</v>
       </c>
       <c r="V120" s="5"/>
       <c r="W120" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.000000000000002</v>
       </c>
       <c r="X120" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.5305015225942693</v>
       </c>
       <c r="Y120" s="1">
@@ -14851,14 +15186,17 @@
       </c>
       <c r="AI120" s="1"/>
       <c r="AJ120" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>230</v>
       </c>
       <c r="AK120" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL120" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL120" s="1">
+        <f t="shared" si="43"/>
+        <v>649.23701818181814</v>
+      </c>
       <c r="AM120" s="1"/>
       <c r="AN120" s="1"/>
       <c r="AO120" s="1"/>
@@ -14889,7 +15227,7 @@
       <c r="J121" s="10"/>
       <c r="K121" s="10"/>
       <c r="L121" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M121" s="10"/>
@@ -14900,25 +15238,25 @@
       <c r="P121" s="10"/>
       <c r="Q121" s="10"/>
       <c r="R121" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S121" s="12"/>
       <c r="T121" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U121" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V121" s="5"/>
       <c r="W121" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X121" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y121" s="10">
@@ -14955,14 +15293,17 @@
         <v>43</v>
       </c>
       <c r="AJ121" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK121" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL121" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL121" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM121" s="1"/>
       <c r="AN121" s="1"/>
       <c r="AO121" s="1"/>
@@ -15005,7 +15346,7 @@
         <v>1.3</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.10799999999999987</v>
       </c>
       <c r="M122" s="1"/>
@@ -15016,25 +15357,25 @@
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.28159999999999996</v>
       </c>
       <c r="S122" s="5"/>
       <c r="T122" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U122" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V122" s="5"/>
       <c r="W122" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>104.69105113636365</v>
       </c>
       <c r="X122" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>104.69105113636365</v>
       </c>
       <c r="Y122" s="1">
@@ -15071,14 +15412,17 @@
         <v>185</v>
       </c>
       <c r="AJ122" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK122" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL122" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL122" s="1">
+        <f t="shared" si="43"/>
+        <v>7.1804727272727273</v>
+      </c>
       <c r="AM122" s="1"/>
       <c r="AN122" s="1"/>
       <c r="AO122" s="1"/>
@@ -15121,7 +15465,7 @@
         <v>369</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-27</v>
       </c>
       <c r="M123" s="1"/>
@@ -15132,19 +15476,19 @@
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>68.400000000000006</v>
       </c>
       <c r="S123" s="5">
-        <f t="shared" ref="S123" si="53">12*R123-Q123-P123-O123-F123</f>
+        <f t="shared" ref="S123" si="55">12*R123-Q123-P123-O123-F123</f>
         <v>393.74400000000003</v>
       </c>
       <c r="T123" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>393.74400000000003</v>
       </c>
       <c r="U123" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>145.21278720000001</v>
       </c>
       <c r="V123" s="5">
@@ -15152,11 +15496,11 @@
         <v>248.53121280000002</v>
       </c>
       <c r="W123" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X123" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>6.2435087719298243</v>
       </c>
       <c r="Y123" s="1">
@@ -15191,14 +15535,17 @@
       </c>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>41</v>
       </c>
       <c r="AK123" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>70</v>
       </c>
-      <c r="AL123" s="1"/>
+      <c r="AL123" s="1">
+        <f t="shared" si="43"/>
+        <v>453.59999999999997</v>
+      </c>
       <c r="AM123" s="1"/>
       <c r="AN123" s="1"/>
       <c r="AO123" s="1"/>
@@ -15229,7 +15576,7 @@
       <c r="J124" s="10"/>
       <c r="K124" s="10"/>
       <c r="L124" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M124" s="10"/>
@@ -15240,25 +15587,25 @@
       <c r="P124" s="10"/>
       <c r="Q124" s="10"/>
       <c r="R124" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S124" s="12"/>
       <c r="T124" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U124" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V124" s="5"/>
       <c r="W124" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X124" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y124" s="10">
@@ -15295,14 +15642,17 @@
         <v>43</v>
       </c>
       <c r="AJ124" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK124" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL124" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL124" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM124" s="1"/>
       <c r="AN124" s="1"/>
       <c r="AO124" s="1"/>
@@ -15345,7 +15695,7 @@
         <v>378</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-46</v>
       </c>
       <c r="M125" s="1"/>
@@ -15356,7 +15706,7 @@
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>66.400000000000006</v>
       </c>
       <c r="S125" s="5">
@@ -15364,11 +15714,11 @@
         <v>365.80000000000007</v>
       </c>
       <c r="T125" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>365.80000000000007</v>
       </c>
       <c r="U125" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>134.90704000000002</v>
       </c>
       <c r="V125" s="5">
@@ -15376,11 +15726,11 @@
         <v>230.89296000000004</v>
       </c>
       <c r="W125" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X125" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>6.4909638554216862</v>
       </c>
       <c r="Y125" s="1">
@@ -15415,14 +15765,17 @@
       </c>
       <c r="AI125" s="1"/>
       <c r="AJ125" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>38</v>
       </c>
       <c r="AK125" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>65</v>
       </c>
-      <c r="AL125" s="1"/>
+      <c r="AL125" s="1">
+        <f t="shared" si="43"/>
+        <v>456.0181818181818</v>
+      </c>
       <c r="AM125" s="1"/>
       <c r="AN125" s="1"/>
       <c r="AO125" s="1"/>
@@ -15453,7 +15806,7 @@
       <c r="J126" s="10"/>
       <c r="K126" s="10"/>
       <c r="L126" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M126" s="10"/>
@@ -15464,25 +15817,25 @@
       <c r="P126" s="10"/>
       <c r="Q126" s="10"/>
       <c r="R126" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S126" s="12"/>
       <c r="T126" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U126" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V126" s="5"/>
       <c r="W126" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X126" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y126" s="10">
@@ -15519,14 +15872,17 @@
         <v>43</v>
       </c>
       <c r="AJ126" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK126" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL126" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL126" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM126" s="1"/>
       <c r="AN126" s="1"/>
       <c r="AO126" s="1"/>
@@ -15569,7 +15925,7 @@
         <v>217.5</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-39.199999999999989</v>
       </c>
       <c r="M127" s="1"/>
@@ -15580,28 +15936,28 @@
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>35.660000000000004</v>
       </c>
       <c r="S127" s="5">
-        <f t="shared" ref="S127" si="54">12*R127-Q127-P127-O127-F127</f>
+        <f t="shared" ref="S127" si="56">12*R127-Q127-P127-O127-F127</f>
         <v>199.48300000000006</v>
       </c>
       <c r="T127" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>199.48300000000006</v>
       </c>
       <c r="U127" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>199.48300000000006</v>
       </c>
       <c r="V127" s="5"/>
       <c r="W127" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X127" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>6.4059730790802014</v>
       </c>
       <c r="Y127" s="1">
@@ -15636,14 +15992,17 @@
       </c>
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>199</v>
       </c>
       <c r="AK127" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL127" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL127" s="1">
+        <f t="shared" si="43"/>
+        <v>249.31963636363639</v>
+      </c>
       <c r="AM127" s="1"/>
       <c r="AN127" s="1"/>
       <c r="AO127" s="1"/>
@@ -15684,7 +16043,7 @@
         <v>105</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-29.945999999999998</v>
       </c>
       <c r="M128" s="1"/>
@@ -15695,25 +16054,25 @@
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>15.0108</v>
       </c>
       <c r="S128" s="5"/>
       <c r="T128" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U128" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V128" s="5"/>
       <c r="W128" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.521184746982174</v>
       </c>
       <c r="X128" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>12.521184746982174</v>
       </c>
       <c r="Y128" s="1">
@@ -15748,14 +16107,17 @@
       </c>
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK128" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL128" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL128" s="1">
+        <f t="shared" si="43"/>
+        <v>126.14050909090906</v>
+      </c>
       <c r="AM128" s="1"/>
       <c r="AN128" s="1"/>
       <c r="AO128" s="1"/>
@@ -15786,7 +16148,7 @@
       <c r="J129" s="10"/>
       <c r="K129" s="10"/>
       <c r="L129" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M129" s="10"/>
@@ -15797,25 +16159,25 @@
       <c r="P129" s="10"/>
       <c r="Q129" s="10"/>
       <c r="R129" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S129" s="12"/>
       <c r="T129" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U129" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V129" s="5"/>
       <c r="W129" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X129" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y129" s="10">
@@ -15852,14 +16214,17 @@
         <v>43</v>
       </c>
       <c r="AJ129" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK129" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL129" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL129" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM129" s="1"/>
       <c r="AN129" s="1"/>
       <c r="AO129" s="1"/>
@@ -15890,7 +16255,7 @@
       <c r="J130" s="10"/>
       <c r="K130" s="10"/>
       <c r="L130" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M130" s="10"/>
@@ -15901,25 +16266,25 @@
       <c r="P130" s="10"/>
       <c r="Q130" s="10"/>
       <c r="R130" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S130" s="12"/>
       <c r="T130" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U130" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V130" s="5"/>
       <c r="W130" s="1" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X130" s="10" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y130" s="10">
@@ -15956,14 +16321,17 @@
         <v>43</v>
       </c>
       <c r="AJ130" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK130" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL130" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL130" s="1">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
       <c r="AM130" s="1"/>
       <c r="AN130" s="1"/>
       <c r="AO130" s="1"/>
@@ -16006,7 +16374,7 @@
         <v>371.55</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>9.6789999999999736</v>
       </c>
       <c r="M131" s="1"/>
@@ -16017,28 +16385,28 @@
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
       <c r="R131" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>76.245800000000003</v>
       </c>
       <c r="S131" s="5">
-        <f t="shared" ref="S131:S139" si="55">12*R131-Q131-P131-O131-F131</f>
+        <f t="shared" ref="S131:S139" si="57">12*R131-Q131-P131-O131-F131</f>
         <v>294.32349999999991</v>
       </c>
       <c r="T131" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>294.32349999999991</v>
       </c>
       <c r="U131" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>294.32349999999991</v>
       </c>
       <c r="V131" s="5"/>
       <c r="W131" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12.000000000000002</v>
       </c>
       <c r="X131" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>8.1398070451093716</v>
       </c>
       <c r="Y131" s="1">
@@ -16073,14 +16441,17 @@
       </c>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>294</v>
       </c>
       <c r="AK131" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL131" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL131" s="1">
+        <f t="shared" si="43"/>
+        <v>427.68600000000004</v>
+      </c>
       <c r="AM131" s="1"/>
       <c r="AN131" s="1"/>
       <c r="AO131" s="1"/>
@@ -16123,7 +16494,7 @@
         <v>441.82</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>8.8480000000000132</v>
       </c>
       <c r="M132" s="1"/>
@@ -16134,19 +16505,19 @@
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
       <c r="R132" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>90.133600000000001</v>
       </c>
       <c r="S132" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>315.75539999999995</v>
       </c>
       <c r="T132" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>315.75539999999995</v>
       </c>
       <c r="U132" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>116.45059151999999</v>
       </c>
       <c r="V132" s="5">
@@ -16154,11 +16525,11 @@
         <v>199.30480847999996</v>
       </c>
       <c r="W132" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X132" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>8.496806962109579</v>
       </c>
       <c r="Y132" s="1">
@@ -16193,14 +16564,17 @@
       </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>116</v>
       </c>
       <c r="AK132" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>199</v>
       </c>
-      <c r="AL132" s="1"/>
+      <c r="AL132" s="1">
+        <f t="shared" si="43"/>
+        <v>565.91500000000008</v>
+      </c>
       <c r="AM132" s="1"/>
       <c r="AN132" s="1"/>
       <c r="AO132" s="1"/>
@@ -16243,7 +16617,7 @@
         <v>129.35</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-6.4879999999999995</v>
       </c>
       <c r="M133" s="1"/>
@@ -16254,28 +16628,28 @@
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
       <c r="R133" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>24.572399999999998</v>
       </c>
       <c r="S133" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>54.690799999999967</v>
       </c>
       <c r="T133" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>54.690799999999967</v>
       </c>
       <c r="U133" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>54.690799999999967</v>
       </c>
       <c r="V133" s="5"/>
       <c r="W133" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>12</v>
       </c>
       <c r="X133" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>9.7742996207126698</v>
       </c>
       <c r="Y133" s="1">
@@ -16310,14 +16684,17 @@
       </c>
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>55</v>
       </c>
       <c r="AK133" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL133" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL133" s="1">
+        <f t="shared" si="43"/>
+        <v>195.86369090909093</v>
+      </c>
       <c r="AM133" s="1"/>
       <c r="AN133" s="1"/>
       <c r="AO133" s="1"/>
@@ -16361,7 +16738,7 @@
         <v>1398.5</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" ref="L134:L142" si="56">E134-K134</f>
+        <f t="shared" ref="L134:L142" si="58">E134-K134</f>
         <v>-427.25400000000002</v>
       </c>
       <c r="M134" s="1"/>
@@ -16372,25 +16749,25 @@
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1">
-        <f t="shared" ref="R134:R142" si="57">E134/5</f>
+        <f t="shared" ref="R134:R142" si="59">E134/5</f>
         <v>194.2492</v>
       </c>
       <c r="S134" s="5"/>
       <c r="T134" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U134" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V134" s="5"/>
       <c r="W134" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14.202339057252232</v>
       </c>
       <c r="X134" s="1">
-        <f t="shared" ref="X134:X142" si="58">(F134+O134+P134+Q134)/R134</f>
+        <f t="shared" ref="X134:X142" si="60">(F134+O134+P134+Q134)/R134</f>
         <v>14.202339057252232</v>
       </c>
       <c r="Y134" s="1">
@@ -16427,14 +16804,17 @@
         <v>186</v>
       </c>
       <c r="AJ134" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK134" s="1">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AL134" s="1"/>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AL134" s="1">
+        <f t="shared" si="43"/>
+        <v>1041.0284181818183</v>
+      </c>
       <c r="AM134" s="1"/>
       <c r="AN134" s="1"/>
       <c r="AO134" s="1"/>
@@ -16477,7 +16857,7 @@
         <v>432</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-13</v>
       </c>
       <c r="M135" s="1"/>
@@ -16488,11 +16868,11 @@
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1">
+        <f t="shared" si="59"/>
+        <v>83.8</v>
+      </c>
+      <c r="S135" s="5">
         <f t="shared" si="57"/>
-        <v>83.8</v>
-      </c>
-      <c r="S135" s="5">
-        <f t="shared" si="55"/>
         <v>527.81199999999978</v>
       </c>
       <c r="T135" s="5">
@@ -16500,19 +16880,19 @@
         <v>506.44299999999976</v>
       </c>
       <c r="U135" s="5">
-        <f t="shared" ref="U135:U142" si="59">T135-V135</f>
+        <f t="shared" ref="U135:U142" si="61">T135-V135</f>
         <v>186.77617839999994</v>
       </c>
       <c r="V135" s="5">
-        <f t="shared" ref="V135:V137" si="60">T135*$V$1</f>
+        <f t="shared" ref="V135:V137" si="62">T135*$V$1</f>
         <v>319.66682159999982</v>
       </c>
       <c r="W135" s="1">
-        <f t="shared" ref="W135:W142" si="61">(F135+O135+P135+Q135+T135)/R135</f>
+        <f t="shared" ref="W135:W142" si="63">(F135+O135+P135+Q135+T135)/R135</f>
         <v>11.744999999999999</v>
       </c>
       <c r="X135" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>5.7015274463007177</v>
       </c>
       <c r="Y135" s="1">
@@ -16547,14 +16927,17 @@
       </c>
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1">
-        <f t="shared" ref="AJ135:AJ142" si="62">ROUND(G135*U135,0)</f>
+        <f t="shared" ref="AJ135:AJ142" si="64">ROUND(G135*U135,0)</f>
         <v>56</v>
       </c>
       <c r="AK135" s="1">
-        <f t="shared" ref="AK135:AK142" si="63">ROUND(G135*V135,0)</f>
+        <f t="shared" ref="AK135:AK142" si="65">ROUND(G135*V135,0)</f>
         <v>96</v>
       </c>
-      <c r="AL135" s="1"/>
+      <c r="AL135" s="1">
+        <f t="shared" ref="AL135:AL142" si="66">(SUM(Y135:AH135)+R135)/11*7</f>
+        <v>455.76363636363635</v>
+      </c>
       <c r="AM135" s="1"/>
       <c r="AN135" s="1"/>
       <c r="AO135" s="1"/>
@@ -16597,7 +16980,7 @@
         <v>368</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-13</v>
       </c>
       <c r="M136" s="1"/>
@@ -16608,31 +16991,31 @@
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
       <c r="R136" s="1">
+        <f t="shared" si="59"/>
+        <v>71</v>
+      </c>
+      <c r="S136" s="5">
         <f t="shared" si="57"/>
-        <v>71</v>
-      </c>
-      <c r="S136" s="5">
-        <f t="shared" si="55"/>
         <v>437.79999999999995</v>
       </c>
       <c r="T136" s="5">
-        <f t="shared" ref="T136:T142" si="64">S136</f>
+        <f t="shared" ref="T136:T142" si="67">S136</f>
         <v>437.79999999999995</v>
       </c>
       <c r="U136" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>161.46064000000001</v>
       </c>
       <c r="V136" s="5">
+        <f t="shared" si="62"/>
+        <v>276.33935999999994</v>
+      </c>
+      <c r="W136" s="1">
+        <f t="shared" si="63"/>
+        <v>12</v>
+      </c>
+      <c r="X136" s="1">
         <f t="shared" si="60"/>
-        <v>276.33935999999994</v>
-      </c>
-      <c r="W136" s="1">
-        <f t="shared" si="61"/>
-        <v>12</v>
-      </c>
-      <c r="X136" s="1">
-        <f t="shared" si="58"/>
         <v>5.8338028169014082</v>
       </c>
       <c r="Y136" s="1">
@@ -16667,14 +17050,17 @@
       </c>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>48</v>
       </c>
       <c r="AK136" s="1">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>83</v>
       </c>
-      <c r="AL136" s="1"/>
+      <c r="AL136" s="1">
+        <f t="shared" si="66"/>
+        <v>367.18181818181819</v>
+      </c>
       <c r="AM136" s="1"/>
       <c r="AN136" s="1"/>
       <c r="AO136" s="1"/>
@@ -16717,7 +17103,7 @@
         <v>280.3</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>10.485000000000014</v>
       </c>
       <c r="M137" s="1"/>
@@ -16728,31 +17114,31 @@
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
       <c r="R137" s="1">
+        <f t="shared" si="59"/>
+        <v>58.157000000000004</v>
+      </c>
+      <c r="S137" s="5">
         <f t="shared" si="57"/>
-        <v>58.157000000000004</v>
-      </c>
-      <c r="S137" s="5">
-        <f t="shared" si="55"/>
         <v>306.40439999999984</v>
       </c>
       <c r="T137" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>306.40439999999984</v>
       </c>
       <c r="U137" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>113.00194271999996</v>
       </c>
       <c r="V137" s="5">
+        <f t="shared" si="62"/>
+        <v>193.40245727999988</v>
+      </c>
+      <c r="W137" s="1">
+        <f t="shared" si="63"/>
+        <v>12</v>
+      </c>
+      <c r="X137" s="1">
         <f t="shared" si="60"/>
-        <v>193.40245727999988</v>
-      </c>
-      <c r="W137" s="1">
-        <f t="shared" si="61"/>
-        <v>12</v>
-      </c>
-      <c r="X137" s="1">
-        <f t="shared" si="58"/>
         <v>6.7314269993294049</v>
       </c>
       <c r="Y137" s="1">
@@ -16787,14 +17173,17 @@
       </c>
       <c r="AI137" s="1"/>
       <c r="AJ137" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>113</v>
       </c>
       <c r="AK137" s="1">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>193</v>
       </c>
-      <c r="AL137" s="1"/>
+      <c r="AL137" s="1">
+        <f t="shared" si="66"/>
+        <v>386.40687272727274</v>
+      </c>
       <c r="AM137" s="1"/>
       <c r="AN137" s="1"/>
       <c r="AO137" s="1"/>
@@ -16837,7 +17226,7 @@
         <v>296</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-4</v>
       </c>
       <c r="M138" s="1"/>
@@ -16848,28 +17237,28 @@
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
       <c r="R138" s="1">
+        <f t="shared" si="59"/>
+        <v>58.4</v>
+      </c>
+      <c r="S138" s="5">
         <f t="shared" si="57"/>
-        <v>58.4</v>
-      </c>
-      <c r="S138" s="5">
-        <f t="shared" si="55"/>
         <v>198.22199999999964</v>
       </c>
       <c r="T138" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>198.22199999999964</v>
       </c>
       <c r="U138" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>198.22199999999964</v>
       </c>
       <c r="V138" s="5"/>
       <c r="W138" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="X138" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>8.605787671232882</v>
       </c>
       <c r="Y138" s="1">
@@ -16904,14 +17293,17 @@
       </c>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>59</v>
       </c>
       <c r="AK138" s="1">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AL138" s="1"/>
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL138" s="1">
+        <f t="shared" si="66"/>
+        <v>374.56363636363636</v>
+      </c>
       <c r="AM138" s="1"/>
       <c r="AN138" s="1"/>
       <c r="AO138" s="1"/>
@@ -16954,7 +17346,7 @@
         <v>61</v>
       </c>
       <c r="L139" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-10</v>
       </c>
       <c r="M139" s="1"/>
@@ -16965,28 +17357,28 @@
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
       <c r="R139" s="1">
+        <f t="shared" si="59"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="S139" s="5">
         <f t="shared" si="57"/>
-        <v>10.199999999999999</v>
-      </c>
-      <c r="S139" s="5">
-        <f t="shared" si="55"/>
         <v>21.399999999999991</v>
       </c>
       <c r="T139" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>21.399999999999991</v>
       </c>
       <c r="U139" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>21.399999999999991</v>
       </c>
       <c r="V139" s="5"/>
       <c r="W139" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="X139" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>9.9019607843137258</v>
       </c>
       <c r="Y139" s="1">
@@ -17021,14 +17413,17 @@
       </c>
       <c r="AI139" s="1"/>
       <c r="AJ139" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>3</v>
       </c>
       <c r="AK139" s="1">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AL139" s="1"/>
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL139" s="1">
+        <f t="shared" si="66"/>
+        <v>45.309090909090912</v>
+      </c>
       <c r="AM139" s="1"/>
       <c r="AN139" s="1"/>
       <c r="AO139" s="1"/>
@@ -17059,7 +17454,7 @@
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M140" s="1"/>
@@ -17070,25 +17465,25 @@
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
       <c r="R140" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S140" s="5"/>
       <c r="T140" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="U140" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="V140" s="5"/>
       <c r="W140" s="1" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X140" s="1" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y140" s="1">
@@ -17125,14 +17520,17 @@
         <v>180</v>
       </c>
       <c r="AJ140" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AK140" s="1">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AL140" s="1"/>
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL140" s="1">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="AM140" s="1"/>
       <c r="AN140" s="1"/>
       <c r="AO140" s="1"/>
@@ -17163,7 +17561,7 @@
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M141" s="1"/>
@@ -17174,25 +17572,25 @@
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
       <c r="R141" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S141" s="5"/>
       <c r="T141" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="U141" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="V141" s="5"/>
       <c r="W141" s="1" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X141" s="1" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y141" s="1">
@@ -17229,14 +17627,17 @@
         <v>180</v>
       </c>
       <c r="AJ141" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AK141" s="1">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AL141" s="1"/>
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL141" s="1">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="AM141" s="1"/>
       <c r="AN141" s="1"/>
       <c r="AO141" s="1"/>
@@ -17267,7 +17668,7 @@
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M142" s="1"/>
@@ -17278,25 +17679,25 @@
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
       <c r="R142" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S142" s="5"/>
       <c r="T142" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="U142" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="V142" s="5"/>
       <c r="W142" s="1" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X142" s="1" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y142" s="1">
@@ -17333,14 +17734,17 @@
         <v>180</v>
       </c>
       <c r="AJ142" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AK142" s="1">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AL142" s="1"/>
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="AL142" s="1">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="AM142" s="1"/>
       <c r="AN142" s="1"/>
       <c r="AO142" s="1"/>
